--- a/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D0E2E06-4772-435E-8DBB-F0478CC0DD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{75C5BC4E-D399-4E76-97AB-82BDB6CD9012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="70" r:id="rId1"/>
@@ -1261,52 +1261,52 @@
     <t>grid_node</t>
   </si>
   <si>
-    <t>p_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>p_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>p_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>p_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>p_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>p_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>p_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>p_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>p_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>p_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>p_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>p_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>p_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>p_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>p_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>p_w203673991-400_IND</t>
+    <t>p_Wardha_IND</t>
+  </si>
+  <si>
+    <t>p_Indore_IND</t>
+  </si>
+  <si>
+    <t>p_Solapur_IND</t>
+  </si>
+  <si>
+    <t>p_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>p_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>p_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>p_Korba_IND</t>
+  </si>
+  <si>
+    <t>p_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>p_Moga_IND</t>
+  </si>
+  <si>
+    <t>p_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>p_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>p_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>p_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>p_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>p_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>p_Tezpur_IND</t>
   </si>
   <si>
     <t>rez_spv_IND_001</t>
@@ -1906,52 +1906,52 @@
     <t>region_com</t>
   </si>
   <si>
-    <t>e_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>e_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>e_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>e_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>e_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>e_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>e_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>e_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>e_w203673991-400_IND</t>
+    <t>e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Indore_IND</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND</t>
+  </si>
+  <si>
+    <t>e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_Moga_IND</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>e_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>e_Tezpur_IND</t>
   </si>
   <si>
     <t>elc_spv_IND_001</t>
@@ -2470,52 +2470,52 @@
     <t>lng</t>
   </si>
   <si>
-    <t>IND-e_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>IND-e_w203673991-400_IND</t>
+    <t>IND-e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Indore_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Korba_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Moga_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>IND-e_Tezpur_IND</t>
   </si>
   <si>
     <t>IND-elc_spv_IND_001</t>
@@ -24146,7 +24146,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2460BD41-8D6A-42DA-A395-6E0C64C58F9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D6476-3BE3-49C5-852E-DD39B93F3778}">
   <dimension ref="B9:H195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -27884,7 +27884,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85FEAD32-5DA3-4689-9FF8-816481476390}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6138FA05-A206-425B-A6DD-FC1A4B33E2EA}">
   <dimension ref="B9:L195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A92A4CD-0F62-42E1-B012-D424330BA4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369A4AC9-8133-4000-9FE5-3CC8371F2DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3966,7 +3966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF0B5AD-A1E1-42EB-9531-825A30E3DAC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B56A19-E4A2-493B-A5F4-5C588B6D60BA}">
   <dimension ref="B9:L195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -31546,7 +31546,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA13FD73-828D-42F1-96CE-963352AE5D63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB5B0B3-985E-4A14-8D1D-1181F50E63DC}">
   <dimension ref="B9:H195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan10/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369A4AC9-8133-4000-9FE5-3CC8371F2DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A2A386-0C55-468C-B70B-9A68A254425D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7119" uniqueCount="985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7108" uniqueCount="981">
   <si>
     <t>Unit</t>
   </si>
@@ -1756,9 +1756,6 @@
     <t>rez_won_IND_066</t>
   </si>
   <si>
-    <t>rez_won_IND_067</t>
-  </si>
-  <si>
     <t>rez_wof_IND_001</t>
   </si>
   <si>
@@ -1867,51 +1864,48 @@
     <t>Assam</t>
   </si>
   <si>
+    <t>Arunachal Pradesh</t>
+  </si>
+  <si>
+    <t>Meghalaya</t>
+  </si>
+  <si>
+    <t>Mizoram</t>
+  </si>
+  <si>
+    <t>Tripura</t>
+  </si>
+  <si>
+    <t>Nagaland</t>
+  </si>
+  <si>
+    <t>Manipur</t>
+  </si>
+  <si>
+    <t>Bihar</t>
+  </si>
+  <si>
+    <t>Jharkhand</t>
+  </si>
+  <si>
+    <t>Odisha</t>
+  </si>
+  <si>
+    <t>Kerala</t>
+  </si>
+  <si>
+    <t>Telangana</t>
+  </si>
+  <si>
+    <t>Karnataka</t>
+  </si>
+  <si>
     <t>Jammu and Kashmir</t>
   </si>
   <si>
     <t>Haryana</t>
   </si>
   <si>
-    <t>Uttarakhand</t>
-  </si>
-  <si>
-    <t>Bihar</t>
-  </si>
-  <si>
-    <t>Jharkhand</t>
-  </si>
-  <si>
-    <t>Manipur</t>
-  </si>
-  <si>
-    <t>Nagaland</t>
-  </si>
-  <si>
-    <t>Meghalaya</t>
-  </si>
-  <si>
-    <t>Mizoram</t>
-  </si>
-  <si>
-    <t>Tripura</t>
-  </si>
-  <si>
-    <t>Arunachal Pradesh</t>
-  </si>
-  <si>
-    <t>Odisha</t>
-  </si>
-  <si>
-    <t>Karnataka</t>
-  </si>
-  <si>
-    <t>Telangana</t>
-  </si>
-  <si>
-    <t>Kerala</t>
-  </si>
-  <si>
     <t>Delhi</t>
   </si>
   <si>
@@ -2401,9 +2395,6 @@
     <t>elc_won_IND_066</t>
   </si>
   <si>
-    <t>elc_won_IND_067</t>
-  </si>
-  <si>
     <t>elc_wof_IND_001</t>
   </si>
   <si>
@@ -2963,9 +2954,6 @@
   </si>
   <si>
     <t>IND-elc_won_IND_066</t>
-  </si>
-  <si>
-    <t>IND-elc_won_IND_067</t>
   </si>
   <si>
     <t>IND-elc_wof_IND_001</t>
@@ -3966,8 +3954,8 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B56A19-E4A2-493B-A5F4-5C588B6D60BA}">
-  <dimension ref="B9:L195"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90BF5BF4-DFF9-46BB-B877-7BEE4915D932}">
+  <dimension ref="B9:L194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="9" spans="2:12">
@@ -4024,19 +4012,19 @@
         <v>397</v>
       </c>
       <c r="G11" t="s">
+        <v>581</v>
+      </c>
+      <c r="H11" t="s">
         <v>582</v>
       </c>
-      <c r="H11" t="s">
-        <v>583</v>
-      </c>
       <c r="J11" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K11" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L11" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="12" spans="2:12">
@@ -4053,19 +4041,19 @@
         <v>398</v>
       </c>
       <c r="G12" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H12" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J12" t="s">
+        <v>609</v>
+      </c>
+      <c r="K12" t="s">
         <v>611</v>
       </c>
-      <c r="K12" t="s">
-        <v>613</v>
-      </c>
       <c r="L12" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="13" spans="2:12">
@@ -4082,19 +4070,19 @@
         <v>399</v>
       </c>
       <c r="G13" t="s">
+        <v>581</v>
+      </c>
+      <c r="H13" t="s">
         <v>582</v>
       </c>
-      <c r="H13" t="s">
-        <v>583</v>
-      </c>
       <c r="J13" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K13" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="L13" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="14" spans="2:12">
@@ -4111,19 +4099,19 @@
         <v>400</v>
       </c>
       <c r="G14" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H14" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J14" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K14" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="L14" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="15" spans="2:12">
@@ -4140,19 +4128,19 @@
         <v>401</v>
       </c>
       <c r="G15" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H15" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J15" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K15" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="L15" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -4169,19 +4157,19 @@
         <v>402</v>
       </c>
       <c r="G16" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H16" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J16" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K16" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="L16" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -4198,19 +4186,19 @@
         <v>403</v>
       </c>
       <c r="G17" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H17" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="J17" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K17" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="L17" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="18" spans="2:12">
@@ -4227,19 +4215,19 @@
         <v>404</v>
       </c>
       <c r="G18" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H18" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J18" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K18" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="L18" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="19" spans="2:12">
@@ -4256,19 +4244,19 @@
         <v>405</v>
       </c>
       <c r="G19" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H19" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J19" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K19" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="L19" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -4285,19 +4273,19 @@
         <v>406</v>
       </c>
       <c r="G20" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H20" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J20" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K20" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="L20" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -4314,19 +4302,19 @@
         <v>407</v>
       </c>
       <c r="G21" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H21" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J21" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K21" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="L21" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="22" spans="2:12">
@@ -4343,19 +4331,19 @@
         <v>408</v>
       </c>
       <c r="G22" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H22" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J22" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K22" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="L22" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="23" spans="2:12">
@@ -4372,19 +4360,19 @@
         <v>409</v>
       </c>
       <c r="G23" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H23" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="J23" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K23" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="L23" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="24" spans="2:12">
@@ -4401,19 +4389,19 @@
         <v>410</v>
       </c>
       <c r="G24" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H24" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J24" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K24" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="L24" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -4430,19 +4418,19 @@
         <v>411</v>
       </c>
       <c r="G25" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H25" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J25" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K25" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="L25" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -4459,19 +4447,19 @@
         <v>412</v>
       </c>
       <c r="G26" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H26" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="J26" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K26" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="L26" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -4488,19 +4476,19 @@
         <v>413</v>
       </c>
       <c r="G27" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H27" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="J27" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K27" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="L27" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="28" spans="2:12">
@@ -4517,19 +4505,19 @@
         <v>414</v>
       </c>
       <c r="G28" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H28" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="J28" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K28" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="L28" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="29" spans="2:12">
@@ -4546,19 +4534,19 @@
         <v>415</v>
       </c>
       <c r="G29" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H29" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="J29" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K29" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="L29" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -4575,19 +4563,19 @@
         <v>416</v>
       </c>
       <c r="G30" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H30" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="J30" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K30" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="L30" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="31" spans="2:12">
@@ -4604,19 +4592,19 @@
         <v>417</v>
       </c>
       <c r="G31" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H31" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="J31" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K31" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="L31" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="32" spans="2:12">
@@ -4633,19 +4621,19 @@
         <v>418</v>
       </c>
       <c r="G32" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H32" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="J32" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K32" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="L32" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -4662,19 +4650,19 @@
         <v>419</v>
       </c>
       <c r="G33" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H33" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="J33" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K33" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="L33" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -4691,19 +4679,19 @@
         <v>420</v>
       </c>
       <c r="G34" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H34" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="J34" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K34" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="L34" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="35" spans="2:12">
@@ -4720,19 +4708,19 @@
         <v>421</v>
       </c>
       <c r="G35" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H35" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="J35" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K35" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="L35" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="36" spans="2:12">
@@ -4749,19 +4737,19 @@
         <v>422</v>
       </c>
       <c r="G36" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H36" t="s">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="J36" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K36" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="L36" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="37" spans="2:12">
@@ -4778,19 +4766,19 @@
         <v>423</v>
       </c>
       <c r="G37" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H37" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="J37" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K37" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="L37" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -4807,19 +4795,19 @@
         <v>424</v>
       </c>
       <c r="G38" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H38" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="J38" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K38" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="L38" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -4836,19 +4824,19 @@
         <v>425</v>
       </c>
       <c r="G39" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H39" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="J39" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K39" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="L39" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="40" spans="2:12">
@@ -4865,19 +4853,19 @@
         <v>426</v>
       </c>
       <c r="G40" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H40" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="J40" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K40" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="L40" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -4894,19 +4882,19 @@
         <v>427</v>
       </c>
       <c r="G41" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H41" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="J41" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K41" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="L41" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="42" spans="2:12">
@@ -4923,19 +4911,19 @@
         <v>428</v>
       </c>
       <c r="G42" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H42" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="J42" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K42" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="L42" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="43" spans="2:12">
@@ -4952,19 +4940,19 @@
         <v>429</v>
       </c>
       <c r="G43" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H43" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="J43" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K43" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="L43" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="44" spans="2:12">
@@ -4981,19 +4969,19 @@
         <v>430</v>
       </c>
       <c r="G44" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H44" t="s">
-        <v>584</v>
+        <v>600</v>
       </c>
       <c r="J44" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K44" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="L44" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="45" spans="2:12">
@@ -5010,19 +4998,19 @@
         <v>431</v>
       </c>
       <c r="G45" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H45" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="J45" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K45" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="L45" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="46" spans="2:12">
@@ -5039,19 +5027,19 @@
         <v>432</v>
       </c>
       <c r="G46" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H46" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
       <c r="J46" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K46" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="L46" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="47" spans="2:12">
@@ -5068,19 +5056,19 @@
         <v>433</v>
       </c>
       <c r="G47" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H47" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="J47" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K47" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="L47" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="48" spans="2:12">
@@ -5097,19 +5085,19 @@
         <v>434</v>
       </c>
       <c r="G48" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H48" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="J48" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K48" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="L48" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="49" spans="2:12">
@@ -5126,19 +5114,19 @@
         <v>435</v>
       </c>
       <c r="G49" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H49" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="J49" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K49" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="L49" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="50" spans="2:12">
@@ -5155,19 +5143,19 @@
         <v>436</v>
       </c>
       <c r="G50" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H50" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="J50" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K50" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="L50" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="51" spans="2:12">
@@ -5184,19 +5172,19 @@
         <v>437</v>
       </c>
       <c r="G51" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H51" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="J51" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K51" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="L51" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="52" spans="2:12">
@@ -5213,19 +5201,19 @@
         <v>438</v>
       </c>
       <c r="G52" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H52" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="J52" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K52" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="L52" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="53" spans="2:12">
@@ -5242,19 +5230,19 @@
         <v>439</v>
       </c>
       <c r="G53" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H53" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="J53" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K53" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="L53" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="54" spans="2:12">
@@ -5271,19 +5259,19 @@
         <v>440</v>
       </c>
       <c r="G54" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H54" t="s">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="J54" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K54" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="L54" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="55" spans="2:12">
@@ -5300,19 +5288,19 @@
         <v>441</v>
       </c>
       <c r="G55" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H55" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="J55" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K55" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="L55" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="56" spans="2:12">
@@ -5329,19 +5317,19 @@
         <v>442</v>
       </c>
       <c r="G56" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H56" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
       <c r="J56" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K56" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="L56" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="57" spans="2:12">
@@ -5358,19 +5346,19 @@
         <v>443</v>
       </c>
       <c r="G57" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H57" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="J57" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K57" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="L57" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="58" spans="2:12">
@@ -5387,19 +5375,19 @@
         <v>444</v>
       </c>
       <c r="G58" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H58" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="J58" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K58" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="L58" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="59" spans="2:12">
@@ -5416,19 +5404,19 @@
         <v>445</v>
       </c>
       <c r="G59" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H59" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="J59" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K59" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="L59" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="60" spans="2:12">
@@ -5445,19 +5433,19 @@
         <v>446</v>
       </c>
       <c r="G60" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H60" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="J60" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K60" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="L60" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="61" spans="2:12">
@@ -5474,19 +5462,19 @@
         <v>447</v>
       </c>
       <c r="G61" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H61" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="J61" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K61" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="L61" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="62" spans="2:12">
@@ -5503,19 +5491,19 @@
         <v>448</v>
       </c>
       <c r="G62" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H62" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="J62" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K62" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="L62" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="63" spans="2:12">
@@ -5532,19 +5520,19 @@
         <v>449</v>
       </c>
       <c r="G63" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H63" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="J63" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K63" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="L63" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="64" spans="2:12">
@@ -5561,19 +5549,19 @@
         <v>450</v>
       </c>
       <c r="G64" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H64" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="J64" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K64" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="L64" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="65" spans="2:12">
@@ -5590,19 +5578,19 @@
         <v>451</v>
       </c>
       <c r="G65" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H65" t="s">
-        <v>602</v>
+        <v>585</v>
       </c>
       <c r="J65" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K65" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="L65" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="66" spans="2:12">
@@ -5619,19 +5607,19 @@
         <v>452</v>
       </c>
       <c r="G66" t="s">
+        <v>581</v>
+      </c>
+      <c r="H66" t="s">
         <v>582</v>
       </c>
-      <c r="H66" t="s">
-        <v>603</v>
-      </c>
       <c r="J66" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K66" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="L66" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="67" spans="2:12">
@@ -5648,19 +5636,19 @@
         <v>453</v>
       </c>
       <c r="G67" t="s">
+        <v>581</v>
+      </c>
+      <c r="H67" t="s">
         <v>582</v>
       </c>
-      <c r="H67" t="s">
-        <v>593</v>
-      </c>
       <c r="J67" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K67" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="L67" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="68" spans="2:12">
@@ -5677,19 +5665,19 @@
         <v>454</v>
       </c>
       <c r="G68" t="s">
+        <v>581</v>
+      </c>
+      <c r="H68" t="s">
         <v>582</v>
       </c>
-      <c r="H68" t="s">
-        <v>593</v>
-      </c>
       <c r="J68" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K68" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="L68" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="69" spans="2:12">
@@ -5706,19 +5694,19 @@
         <v>455</v>
       </c>
       <c r="G69" t="s">
+        <v>581</v>
+      </c>
+      <c r="H69" t="s">
         <v>582</v>
       </c>
-      <c r="H69" t="s">
-        <v>604</v>
-      </c>
       <c r="J69" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K69" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="L69" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="70" spans="2:12">
@@ -5735,19 +5723,19 @@
         <v>456</v>
       </c>
       <c r="G70" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H70" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="J70" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K70" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="L70" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="71" spans="2:12">
@@ -5764,19 +5752,19 @@
         <v>457</v>
       </c>
       <c r="G71" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H71" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="J71" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K71" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="L71" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="72" spans="2:12">
@@ -5793,19 +5781,19 @@
         <v>458</v>
       </c>
       <c r="G72" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H72" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="J72" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K72" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="L72" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="73" spans="2:12">
@@ -5822,19 +5810,19 @@
         <v>459</v>
       </c>
       <c r="G73" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H73" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="J73" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K73" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="L73" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="74" spans="2:12">
@@ -5851,19 +5839,19 @@
         <v>460</v>
       </c>
       <c r="G74" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H74" t="s">
-        <v>605</v>
+        <v>583</v>
       </c>
       <c r="J74" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K74" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="L74" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="75" spans="2:12">
@@ -5880,19 +5868,19 @@
         <v>461</v>
       </c>
       <c r="G75" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H75" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="J75" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K75" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="L75" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="76" spans="2:12">
@@ -5909,19 +5897,19 @@
         <v>462</v>
       </c>
       <c r="G76" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H76" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="J76" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K76" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="L76" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="77" spans="2:12">
@@ -5938,19 +5926,19 @@
         <v>463</v>
       </c>
       <c r="G77" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H77" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="J77" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K77" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="L77" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="78" spans="2:12">
@@ -5967,19 +5955,19 @@
         <v>464</v>
       </c>
       <c r="G78" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H78" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="J78" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K78" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="L78" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="79" spans="2:12">
@@ -5996,19 +5984,19 @@
         <v>465</v>
       </c>
       <c r="G79" t="s">
+        <v>581</v>
+      </c>
+      <c r="H79" t="s">
         <v>582</v>
       </c>
-      <c r="H79" t="s">
-        <v>583</v>
-      </c>
       <c r="J79" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K79" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="L79" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="80" spans="2:12">
@@ -6025,19 +6013,19 @@
         <v>466</v>
       </c>
       <c r="G80" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H80" t="s">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="J80" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K80" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="L80" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="81" spans="2:12">
@@ -6054,19 +6042,19 @@
         <v>467</v>
       </c>
       <c r="G81" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H81" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="J81" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K81" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="L81" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="82" spans="2:12">
@@ -6083,19 +6071,19 @@
         <v>468</v>
       </c>
       <c r="G82" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H82" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="J82" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K82" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="L82" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="83" spans="2:12">
@@ -6112,19 +6100,19 @@
         <v>469</v>
       </c>
       <c r="G83" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H83" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="J83" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K83" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="L83" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="84" spans="2:12">
@@ -6141,19 +6129,19 @@
         <v>470</v>
       </c>
       <c r="G84" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H84" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="J84" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K84" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="L84" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="85" spans="2:12">
@@ -6170,19 +6158,19 @@
         <v>471</v>
       </c>
       <c r="G85" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H85" t="s">
-        <v>606</v>
+        <v>586</v>
       </c>
       <c r="J85" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K85" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="L85" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="86" spans="2:12">
@@ -6199,19 +6187,19 @@
         <v>472</v>
       </c>
       <c r="G86" t="s">
+        <v>581</v>
+      </c>
+      <c r="H86" t="s">
         <v>582</v>
       </c>
-      <c r="H86" t="s">
-        <v>607</v>
-      </c>
       <c r="J86" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K86" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="L86" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="87" spans="2:12">
@@ -6228,19 +6216,19 @@
         <v>473</v>
       </c>
       <c r="G87" t="s">
+        <v>581</v>
+      </c>
+      <c r="H87" t="s">
         <v>582</v>
       </c>
-      <c r="H87" t="s">
-        <v>583</v>
-      </c>
       <c r="J87" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K87" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="L87" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="88" spans="2:12">
@@ -6257,19 +6245,19 @@
         <v>474</v>
       </c>
       <c r="G88" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H88" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="J88" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K88" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="L88" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="89" spans="2:12">
@@ -6286,19 +6274,19 @@
         <v>475</v>
       </c>
       <c r="G89" t="s">
+        <v>581</v>
+      </c>
+      <c r="H89" t="s">
         <v>582</v>
       </c>
-      <c r="H89" t="s">
-        <v>583</v>
-      </c>
       <c r="J89" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K89" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="L89" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="90" spans="2:12">
@@ -6315,19 +6303,19 @@
         <v>476</v>
       </c>
       <c r="G90" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H90" t="s">
-        <v>606</v>
+        <v>586</v>
       </c>
       <c r="J90" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K90" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="L90" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="91" spans="2:12">
@@ -6344,19 +6332,19 @@
         <v>477</v>
       </c>
       <c r="G91" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H91" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="J91" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K91" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="L91" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="92" spans="2:12">
@@ -6373,19 +6361,19 @@
         <v>478</v>
       </c>
       <c r="G92" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H92" t="s">
-        <v>607</v>
+        <v>583</v>
       </c>
       <c r="J92" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K92" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="L92" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="93" spans="2:12">
@@ -6402,19 +6390,19 @@
         <v>479</v>
       </c>
       <c r="G93" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H93" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="J93" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K93" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="L93" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="94" spans="2:12">
@@ -6431,19 +6419,19 @@
         <v>480</v>
       </c>
       <c r="G94" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H94" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J94" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K94" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="L94" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="95" spans="2:12">
@@ -6460,19 +6448,19 @@
         <v>481</v>
       </c>
       <c r="G95" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H95" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="J95" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K95" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="L95" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="96" spans="2:12">
@@ -6489,19 +6477,19 @@
         <v>482</v>
       </c>
       <c r="G96" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H96" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="J96" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K96" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="L96" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="97" spans="2:12">
@@ -6518,19 +6506,19 @@
         <v>483</v>
       </c>
       <c r="G97" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H97" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="J97" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K97" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="L97" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="98" spans="2:12">
@@ -6547,19 +6535,19 @@
         <v>484</v>
       </c>
       <c r="G98" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H98" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="J98" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K98" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="L98" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="99" spans="2:12">
@@ -6576,19 +6564,19 @@
         <v>485</v>
       </c>
       <c r="G99" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H99" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="J99" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K99" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="L99" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="100" spans="2:12">
@@ -6605,19 +6593,19 @@
         <v>486</v>
       </c>
       <c r="G100" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H100" t="s">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="J100" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K100" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="L100" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="101" spans="2:12">
@@ -6634,19 +6622,19 @@
         <v>487</v>
       </c>
       <c r="G101" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H101" t="s">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="J101" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K101" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="L101" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="102" spans="2:12">
@@ -6663,19 +6651,19 @@
         <v>488</v>
       </c>
       <c r="G102" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H102" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="J102" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K102" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="L102" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="103" spans="2:12">
@@ -6692,19 +6680,19 @@
         <v>489</v>
       </c>
       <c r="G103" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H103" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J103" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K103" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="L103" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="104" spans="2:12">
@@ -6721,19 +6709,19 @@
         <v>490</v>
       </c>
       <c r="G104" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H104" t="s">
         <v>606</v>
       </c>
       <c r="J104" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K104" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="L104" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="105" spans="2:12">
@@ -6750,19 +6738,19 @@
         <v>491</v>
       </c>
       <c r="G105" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H105" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="J105" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K105" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="L105" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="106" spans="2:12">
@@ -6779,19 +6767,19 @@
         <v>492</v>
       </c>
       <c r="G106" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H106" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="J106" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K106" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="L106" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="107" spans="2:12">
@@ -6808,19 +6796,19 @@
         <v>493</v>
       </c>
       <c r="G107" t="s">
+        <v>581</v>
+      </c>
+      <c r="H107" t="s">
         <v>582</v>
       </c>
-      <c r="H107" t="s">
-        <v>585</v>
-      </c>
       <c r="J107" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K107" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="L107" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="108" spans="2:12">
@@ -6837,19 +6825,19 @@
         <v>494</v>
       </c>
       <c r="G108" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H108" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="J108" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K108" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="L108" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="109" spans="2:12">
@@ -6866,19 +6854,19 @@
         <v>495</v>
       </c>
       <c r="G109" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H109" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="J109" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K109" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="L109" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="110" spans="2:12">
@@ -6895,19 +6883,19 @@
         <v>496</v>
       </c>
       <c r="G110" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H110" t="s">
         <v>585</v>
       </c>
       <c r="J110" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K110" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="L110" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="111" spans="2:12">
@@ -6924,19 +6912,19 @@
         <v>497</v>
       </c>
       <c r="G111" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H111" t="s">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="J111" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K111" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="L111" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="112" spans="2:12">
@@ -6953,19 +6941,19 @@
         <v>498</v>
       </c>
       <c r="G112" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H112" t="s">
+        <v>601</v>
+      </c>
+      <c r="J112" t="s">
         <v>609</v>
       </c>
-      <c r="J112" t="s">
-        <v>611</v>
-      </c>
       <c r="K112" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="L112" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="113" spans="2:12">
@@ -6982,19 +6970,19 @@
         <v>499</v>
       </c>
       <c r="G113" t="s">
+        <v>581</v>
+      </c>
+      <c r="H113" t="s">
         <v>582</v>
       </c>
-      <c r="H113" t="s">
-        <v>584</v>
-      </c>
       <c r="J113" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K113" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="L113" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="114" spans="2:12">
@@ -7011,19 +6999,19 @@
         <v>500</v>
       </c>
       <c r="G114" t="s">
+        <v>581</v>
+      </c>
+      <c r="H114" t="s">
         <v>582</v>
       </c>
-      <c r="H114" t="s">
-        <v>584</v>
-      </c>
       <c r="J114" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K114" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="L114" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="115" spans="2:12">
@@ -7040,19 +7028,19 @@
         <v>501</v>
       </c>
       <c r="G115" t="s">
+        <v>581</v>
+      </c>
+      <c r="H115" t="s">
         <v>582</v>
       </c>
-      <c r="H115" t="s">
-        <v>584</v>
-      </c>
       <c r="J115" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K115" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="L115" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="116" spans="2:12">
@@ -7069,19 +7057,19 @@
         <v>502</v>
       </c>
       <c r="G116" t="s">
+        <v>581</v>
+      </c>
+      <c r="H116" t="s">
         <v>582</v>
       </c>
-      <c r="H116" t="s">
-        <v>584</v>
-      </c>
       <c r="J116" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K116" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="L116" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="117" spans="2:12">
@@ -7098,19 +7086,19 @@
         <v>503</v>
       </c>
       <c r="G117" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H117" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J117" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K117" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="L117" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="118" spans="2:12">
@@ -7127,19 +7115,19 @@
         <v>504</v>
       </c>
       <c r="G118" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H118" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="J118" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K118" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="L118" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="119" spans="2:12">
@@ -7156,19 +7144,19 @@
         <v>505</v>
       </c>
       <c r="G119" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H119" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="J119" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K119" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="L119" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="120" spans="2:12">
@@ -7185,19 +7173,19 @@
         <v>506</v>
       </c>
       <c r="G120" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H120" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="J120" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K120" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="L120" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="121" spans="2:12">
@@ -7214,19 +7202,19 @@
         <v>507</v>
       </c>
       <c r="G121" t="s">
+        <v>581</v>
+      </c>
+      <c r="H121" t="s">
         <v>582</v>
       </c>
-      <c r="H121" t="s">
-        <v>597</v>
-      </c>
       <c r="J121" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K121" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="L121" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="122" spans="2:12">
@@ -7243,19 +7231,19 @@
         <v>508</v>
       </c>
       <c r="G122" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H122" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="J122" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K122" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="L122" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="123" spans="2:12">
@@ -7272,19 +7260,19 @@
         <v>509</v>
       </c>
       <c r="G123" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H123" t="s">
         <v>585</v>
       </c>
       <c r="J123" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K123" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="L123" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="124" spans="2:12">
@@ -7301,19 +7289,19 @@
         <v>510</v>
       </c>
       <c r="G124" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H124" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="J124" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K124" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="L124" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="125" spans="2:12">
@@ -7330,19 +7318,19 @@
         <v>511</v>
       </c>
       <c r="G125" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H125" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="J125" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K125" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="L125" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="126" spans="2:12">
@@ -7359,19 +7347,19 @@
         <v>512</v>
       </c>
       <c r="G126" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H126" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="J126" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K126" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="L126" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="127" spans="2:12">
@@ -7388,19 +7376,19 @@
         <v>513</v>
       </c>
       <c r="G127" t="s">
+        <v>581</v>
+      </c>
+      <c r="H127" t="s">
         <v>582</v>
       </c>
-      <c r="H127" t="s">
-        <v>592</v>
-      </c>
       <c r="J127" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K127" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="L127" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="128" spans="2:12">
@@ -7417,19 +7405,19 @@
         <v>514</v>
       </c>
       <c r="G128" t="s">
+        <v>581</v>
+      </c>
+      <c r="H128" t="s">
         <v>582</v>
       </c>
-      <c r="H128" t="s">
-        <v>605</v>
-      </c>
       <c r="J128" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K128" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="L128" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="129" spans="2:12">
@@ -7446,19 +7434,19 @@
         <v>515</v>
       </c>
       <c r="G129" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H129" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="J129" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K129" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="L129" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="130" spans="2:12">
@@ -7475,19 +7463,19 @@
         <v>516</v>
       </c>
       <c r="G130" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H130" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="J130" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K130" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="L130" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="131" spans="2:12">
@@ -7504,19 +7492,19 @@
         <v>517</v>
       </c>
       <c r="G131" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H131" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="J131" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K131" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="L131" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="132" spans="2:12">
@@ -7533,19 +7521,19 @@
         <v>518</v>
       </c>
       <c r="G132" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H132" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="J132" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K132" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="L132" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="133" spans="2:12">
@@ -7562,19 +7550,19 @@
         <v>519</v>
       </c>
       <c r="G133" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H133" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="J133" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K133" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="L133" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="134" spans="2:12">
@@ -7591,19 +7579,19 @@
         <v>520</v>
       </c>
       <c r="G134" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H134" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J134" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K134" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="L134" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="135" spans="2:12">
@@ -7620,19 +7608,19 @@
         <v>521</v>
       </c>
       <c r="G135" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H135" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="J135" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K135" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="L135" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="136" spans="2:12">
@@ -7649,19 +7637,19 @@
         <v>522</v>
       </c>
       <c r="G136" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H136" t="s">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="J136" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K136" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="L136" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="137" spans="2:12">
@@ -7678,19 +7666,19 @@
         <v>523</v>
       </c>
       <c r="G137" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H137" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="J137" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K137" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="L137" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="138" spans="2:12">
@@ -7707,19 +7695,19 @@
         <v>524</v>
       </c>
       <c r="G138" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H138" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="J138" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K138" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="L138" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="139" spans="2:12">
@@ -7736,19 +7724,19 @@
         <v>525</v>
       </c>
       <c r="G139" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H139" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="J139" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K139" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="L139" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="140" spans="2:12">
@@ -7765,19 +7753,19 @@
         <v>526</v>
       </c>
       <c r="G140" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H140" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="J140" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K140" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="L140" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="141" spans="2:12">
@@ -7794,19 +7782,19 @@
         <v>527</v>
       </c>
       <c r="G141" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H141" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="J141" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K141" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="L141" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="142" spans="2:12">
@@ -7823,19 +7811,19 @@
         <v>528</v>
       </c>
       <c r="G142" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H142" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J142" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K142" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="L142" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="143" spans="2:12">
@@ -7852,19 +7840,19 @@
         <v>529</v>
       </c>
       <c r="G143" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H143" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="J143" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K143" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="L143" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="144" spans="2:12">
@@ -7881,19 +7869,19 @@
         <v>530</v>
       </c>
       <c r="G144" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H144" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="J144" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K144" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="L144" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="145" spans="2:12">
@@ -7910,19 +7898,19 @@
         <v>531</v>
       </c>
       <c r="G145" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H145" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="J145" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K145" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="L145" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="146" spans="2:12">
@@ -7939,19 +7927,19 @@
         <v>532</v>
       </c>
       <c r="G146" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H146" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="J146" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K146" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="L146" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="147" spans="2:12">
@@ -7968,19 +7956,19 @@
         <v>533</v>
       </c>
       <c r="G147" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H147" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="J147" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K147" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="L147" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="148" spans="2:12">
@@ -7997,19 +7985,19 @@
         <v>534</v>
       </c>
       <c r="G148" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H148" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="J148" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K148" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="L148" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="149" spans="2:12">
@@ -8026,19 +8014,19 @@
         <v>535</v>
       </c>
       <c r="G149" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H149" t="s">
         <v>591</v>
       </c>
       <c r="J149" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K149" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="L149" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="150" spans="2:12">
@@ -8055,19 +8043,19 @@
         <v>536</v>
       </c>
       <c r="G150" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H150" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="J150" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K150" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="L150" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="151" spans="2:12">
@@ -8084,19 +8072,19 @@
         <v>537</v>
       </c>
       <c r="G151" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H151" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="J151" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K151" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="L151" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="152" spans="2:12">
@@ -8113,19 +8101,19 @@
         <v>538</v>
       </c>
       <c r="G152" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H152" t="s">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="J152" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K152" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="L152" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="153" spans="2:12">
@@ -8142,19 +8130,19 @@
         <v>539</v>
       </c>
       <c r="G153" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H153" t="s">
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="J153" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K153" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="L153" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="154" spans="2:12">
@@ -8171,19 +8159,19 @@
         <v>540</v>
       </c>
       <c r="G154" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H154" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="J154" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K154" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="L154" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="155" spans="2:12">
@@ -8200,19 +8188,19 @@
         <v>541</v>
       </c>
       <c r="G155" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H155" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="J155" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K155" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="L155" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="156" spans="2:12">
@@ -8229,19 +8217,19 @@
         <v>542</v>
       </c>
       <c r="G156" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H156" t="s">
-        <v>589</v>
+        <v>606</v>
       </c>
       <c r="J156" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K156" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="L156" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="157" spans="2:12">
@@ -8258,19 +8246,19 @@
         <v>543</v>
       </c>
       <c r="G157" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H157" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J157" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K157" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="L157" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="158" spans="2:12">
@@ -8287,19 +8275,19 @@
         <v>544</v>
       </c>
       <c r="G158" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H158" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="J158" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K158" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="L158" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="159" spans="2:12">
@@ -8316,19 +8304,19 @@
         <v>545</v>
       </c>
       <c r="G159" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H159" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="J159" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K159" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="L159" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="160" spans="2:12">
@@ -8345,19 +8333,19 @@
         <v>546</v>
       </c>
       <c r="G160" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H160" t="s">
         <v>584</v>
       </c>
       <c r="J160" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K160" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="L160" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="161" spans="2:12">
@@ -8374,19 +8362,19 @@
         <v>547</v>
       </c>
       <c r="G161" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H161" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="J161" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K161" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="L161" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="162" spans="2:12">
@@ -8403,19 +8391,19 @@
         <v>548</v>
       </c>
       <c r="G162" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H162" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="J162" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K162" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="L162" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="163" spans="2:12">
@@ -8432,19 +8420,19 @@
         <v>549</v>
       </c>
       <c r="G163" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H163" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J163" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K163" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="L163" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="164" spans="2:12">
@@ -8461,19 +8449,19 @@
         <v>550</v>
       </c>
       <c r="G164" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H164" t="s">
         <v>584</v>
       </c>
       <c r="J164" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K164" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="L164" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="165" spans="2:12">
@@ -8490,19 +8478,19 @@
         <v>551</v>
       </c>
       <c r="G165" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H165" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="J165" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K165" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="L165" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="166" spans="2:12">
@@ -8519,19 +8507,19 @@
         <v>552</v>
       </c>
       <c r="G166" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H166" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="J166" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K166" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="L166" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="167" spans="2:12">
@@ -8548,19 +8536,19 @@
         <v>553</v>
       </c>
       <c r="G167" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H167" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="J167" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K167" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="L167" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="168" spans="2:12">
@@ -8577,19 +8565,19 @@
         <v>554</v>
       </c>
       <c r="G168" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H168" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="J168" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K168" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="L168" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="169" spans="2:12">
@@ -8606,19 +8594,19 @@
         <v>555</v>
       </c>
       <c r="G169" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H169" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="J169" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K169" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="L169" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="170" spans="2:12">
@@ -8635,19 +8623,19 @@
         <v>556</v>
       </c>
       <c r="G170" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H170" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="J170" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K170" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="L170" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="171" spans="2:12">
@@ -8664,19 +8652,19 @@
         <v>557</v>
       </c>
       <c r="G171" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H171" t="s">
-        <v>589</v>
+        <v>608</v>
       </c>
       <c r="J171" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K171" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="L171" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="172" spans="2:12">
@@ -8693,19 +8681,19 @@
         <v>558</v>
       </c>
       <c r="G172" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H172" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J172" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K172" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="L172" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="173" spans="2:12">
@@ -8722,19 +8710,19 @@
         <v>559</v>
       </c>
       <c r="G173" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H173" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J173" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K173" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="L173" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="174" spans="2:12">
@@ -8751,19 +8739,19 @@
         <v>560</v>
       </c>
       <c r="G174" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H174" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J174" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K174" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="L174" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="175" spans="2:12">
@@ -8780,19 +8768,19 @@
         <v>561</v>
       </c>
       <c r="G175" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H175" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J175" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K175" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="L175" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="176" spans="2:12">
@@ -8809,19 +8797,19 @@
         <v>562</v>
       </c>
       <c r="G176" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H176" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J176" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K176" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="L176" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="177" spans="2:12">
@@ -8838,19 +8826,19 @@
         <v>563</v>
       </c>
       <c r="G177" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H177" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J177" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K177" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="L177" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="178" spans="2:12">
@@ -8867,19 +8855,19 @@
         <v>564</v>
       </c>
       <c r="G178" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H178" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J178" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K178" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="L178" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="179" spans="2:12">
@@ -8896,19 +8884,19 @@
         <v>565</v>
       </c>
       <c r="G179" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H179" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J179" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K179" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="L179" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="180" spans="2:12">
@@ -8925,19 +8913,19 @@
         <v>566</v>
       </c>
       <c r="G180" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H180" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J180" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K180" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="L180" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="181" spans="2:12">
@@ -8954,19 +8942,19 @@
         <v>567</v>
       </c>
       <c r="G181" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H181" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J181" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K181" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="L181" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="182" spans="2:12">
@@ -8983,19 +8971,19 @@
         <v>568</v>
       </c>
       <c r="G182" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H182" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J182" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K182" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="L182" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="183" spans="2:12">
@@ -9012,19 +9000,19 @@
         <v>569</v>
       </c>
       <c r="G183" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H183" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J183" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K183" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="L183" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="184" spans="2:12">
@@ -9041,19 +9029,19 @@
         <v>570</v>
       </c>
       <c r="G184" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H184" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J184" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K184" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="L184" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="185" spans="2:12">
@@ -9070,19 +9058,19 @@
         <v>571</v>
       </c>
       <c r="G185" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H185" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J185" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K185" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="L185" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="186" spans="2:12">
@@ -9099,19 +9087,19 @@
         <v>572</v>
       </c>
       <c r="G186" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H186" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J186" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K186" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="L186" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="187" spans="2:12">
@@ -9128,19 +9116,19 @@
         <v>573</v>
       </c>
       <c r="G187" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H187" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J187" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K187" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="L187" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="188" spans="2:12">
@@ -9157,19 +9145,19 @@
         <v>574</v>
       </c>
       <c r="G188" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H188" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J188" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K188" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="L188" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="189" spans="2:12">
@@ -9186,19 +9174,19 @@
         <v>575</v>
       </c>
       <c r="G189" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H189" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J189" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K189" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="L189" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="190" spans="2:12">
@@ -9215,19 +9203,19 @@
         <v>576</v>
       </c>
       <c r="G190" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H190" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J190" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K190" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="L190" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="191" spans="2:12">
@@ -9244,19 +9232,19 @@
         <v>577</v>
       </c>
       <c r="G191" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H191" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J191" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K191" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="L191" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="192" spans="2:12">
@@ -9273,19 +9261,19 @@
         <v>578</v>
       </c>
       <c r="G192" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H192" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J192" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K192" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="L192" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="193" spans="2:12">
@@ -9302,19 +9290,19 @@
         <v>579</v>
       </c>
       <c r="G193" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H193" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J193" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K193" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="L193" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="194" spans="2:12">
@@ -9331,48 +9319,19 @@
         <v>580</v>
       </c>
       <c r="G194" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H194" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J194" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K194" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="L194" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="195" spans="2:12">
-      <c r="B195" t="s">
-        <v>396</v>
-      </c>
-      <c r="C195" t="s">
-        <v>581</v>
-      </c>
-      <c r="D195" t="s">
-        <v>581</v>
-      </c>
-      <c r="F195" t="s">
-        <v>581</v>
-      </c>
-      <c r="G195" t="s">
-        <v>582</v>
-      </c>
-      <c r="H195" t="s">
-        <v>610</v>
-      </c>
-      <c r="J195" t="s">
-        <v>611</v>
-      </c>
-      <c r="K195" t="s">
-        <v>796</v>
-      </c>
-      <c r="L195" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
   </sheetData>
@@ -31546,16 +31505,16 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB5B0B3-985E-4A14-8D1D-1181F50E63DC}">
-  <dimension ref="B9:H195"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AD6825-8B82-4DDF-84D0-3D262CD546E7}">
+  <dimension ref="B9:H194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="9" spans="2:8">
       <c r="B9" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="F9" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="10" spans="2:8">
@@ -31563,19 +31522,19 @@
         <v>389</v>
       </c>
       <c r="C10" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D10" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="F10" t="s">
         <v>389</v>
       </c>
       <c r="G10" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="H10" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="11" spans="2:8">
@@ -31583,19 +31542,19 @@
         <v>397</v>
       </c>
       <c r="C11">
-        <v>20.669102670000001</v>
+        <v>20.669102672493342</v>
       </c>
       <c r="D11">
-        <v>78.492722979999996</v>
+        <v>78.492722981662908</v>
       </c>
       <c r="F11" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="G11">
-        <v>20.669102670000001</v>
+        <v>20.669102672493342</v>
       </c>
       <c r="H11">
-        <v>78.492722979999996</v>
+        <v>78.492722981662908</v>
       </c>
     </row>
     <row r="12" spans="2:8">
@@ -31603,19 +31562,19 @@
         <v>398</v>
       </c>
       <c r="C12">
-        <v>22.908338069999999</v>
+        <v>22.908338070793363</v>
       </c>
       <c r="D12">
-        <v>75.904012760000001</v>
+        <v>75.90401276433046</v>
       </c>
       <c r="F12" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="G12">
-        <v>22.908338069999999</v>
+        <v>22.908338070793363</v>
       </c>
       <c r="H12">
-        <v>75.904012760000001</v>
+        <v>75.90401276433046</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -31623,19 +31582,19 @@
         <v>399</v>
       </c>
       <c r="C13">
-        <v>17.60776027</v>
+        <v>17.607760270934016</v>
       </c>
       <c r="D13">
-        <v>76.05120153</v>
+        <v>76.051201531523105</v>
       </c>
       <c r="F13" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="G13">
-        <v>17.60776027</v>
+        <v>17.607760270934016</v>
       </c>
       <c r="H13">
-        <v>76.05120153</v>
+        <v>76.051201531523105</v>
       </c>
     </row>
     <row r="14" spans="2:8">
@@ -31643,19 +31602,19 @@
         <v>400</v>
       </c>
       <c r="C14">
-        <v>25.957447380000001</v>
+        <v>25.957447383134458</v>
       </c>
       <c r="D14">
-        <v>80.853483650000001</v>
+        <v>80.853483649853217</v>
       </c>
       <c r="F14" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="G14">
-        <v>25.957447380000001</v>
+        <v>25.957447383134458</v>
       </c>
       <c r="H14">
-        <v>80.853483650000001</v>
+        <v>80.853483649853217</v>
       </c>
     </row>
     <row r="15" spans="2:8">
@@ -31663,19 +31622,19 @@
         <v>401</v>
       </c>
       <c r="C15">
-        <v>15.673490340000001</v>
+        <v>15.673490343021944</v>
       </c>
       <c r="D15">
-        <v>78.177770339999995</v>
+        <v>78.177770343689502</v>
       </c>
       <c r="F15" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="G15">
-        <v>15.673490340000001</v>
+        <v>15.673490343021944</v>
       </c>
       <c r="H15">
-        <v>78.177770339999995</v>
+        <v>78.177770343689502</v>
       </c>
     </row>
     <row r="16" spans="2:8">
@@ -31683,19 +31642,19 @@
         <v>402</v>
       </c>
       <c r="C16">
-        <v>22.317293029999998</v>
+        <v>22.317293030637487</v>
       </c>
       <c r="D16">
-        <v>73.377135629999998</v>
+        <v>73.377135632267908</v>
       </c>
       <c r="F16" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="G16">
-        <v>22.317293029999998</v>
+        <v>22.317293030637487</v>
       </c>
       <c r="H16">
-        <v>73.377135629999998</v>
+        <v>73.377135632267908</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -31703,19 +31662,19 @@
         <v>403</v>
       </c>
       <c r="C17">
-        <v>22.27169275</v>
+        <v>22.271692751270525</v>
       </c>
       <c r="D17">
-        <v>82.762172179999993</v>
+        <v>82.762172184031854</v>
       </c>
       <c r="F17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="G17">
-        <v>22.27169275</v>
+        <v>22.271692751270525</v>
       </c>
       <c r="H17">
-        <v>82.762172179999993</v>
+        <v>82.762172184031854</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -31723,19 +31682,19 @@
         <v>404</v>
       </c>
       <c r="C18">
-        <v>26.651351519999999</v>
+        <v>26.651351516019087</v>
       </c>
       <c r="D18">
-        <v>75.665218789999997</v>
+        <v>75.665218786562164</v>
       </c>
       <c r="F18" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="G18">
-        <v>26.651351519999999</v>
+        <v>26.651351516019087</v>
       </c>
       <c r="H18">
-        <v>75.665218789999997</v>
+        <v>75.665218786562164</v>
       </c>
     </row>
     <row r="19" spans="2:8">
@@ -31743,19 +31702,19 @@
         <v>405</v>
       </c>
       <c r="C19">
-        <v>30.784075720000001</v>
+        <v>30.784075715982738</v>
       </c>
       <c r="D19">
-        <v>75.146078509999995</v>
+        <v>75.146078508432495</v>
       </c>
       <c r="F19" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="G19">
-        <v>30.784075720000001</v>
+        <v>30.784075715982738</v>
       </c>
       <c r="H19">
-        <v>75.146078509999995</v>
+        <v>75.146078508432495</v>
       </c>
     </row>
     <row r="20" spans="2:8">
@@ -31763,19 +31722,19 @@
         <v>406</v>
       </c>
       <c r="C20">
-        <v>12.13311356</v>
+        <v>12.133113559842871</v>
       </c>
       <c r="D20">
-        <v>78.030826410000003</v>
+        <v>78.030826414577206</v>
       </c>
       <c r="F20" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="G20">
-        <v>12.13311356</v>
+        <v>12.133113559842871</v>
       </c>
       <c r="H20">
-        <v>78.030826410000003</v>
+        <v>78.030826414577206</v>
       </c>
     </row>
     <row r="21" spans="2:8">
@@ -31783,19 +31742,19 @@
         <v>407</v>
       </c>
       <c r="C21">
-        <v>28.196007550000001</v>
+        <v>28.196007553336685</v>
       </c>
       <c r="D21">
-        <v>77.697852010000005</v>
+        <v>77.697852005819513</v>
       </c>
       <c r="F21" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="G21">
-        <v>28.196007550000001</v>
+        <v>28.196007553336685</v>
       </c>
       <c r="H21">
-        <v>77.697852010000005</v>
+        <v>77.697852005819513</v>
       </c>
     </row>
     <row r="22" spans="2:8">
@@ -31803,19 +31762,19 @@
         <v>408</v>
       </c>
       <c r="C22">
-        <v>23.452485060000001</v>
+        <v>23.452485058949303</v>
       </c>
       <c r="D22">
-        <v>69.59257685</v>
+        <v>69.592576853385523</v>
       </c>
       <c r="F22" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="G22">
-        <v>23.452485060000001</v>
+        <v>23.452485058949303</v>
       </c>
       <c r="H22">
-        <v>69.59257685</v>
+        <v>69.592576853385523</v>
       </c>
     </row>
     <row r="23" spans="2:8">
@@ -31823,19 +31782,19 @@
         <v>409</v>
       </c>
       <c r="C23">
-        <v>22.690868699999999</v>
+        <v>22.690868695213929</v>
       </c>
       <c r="D23">
-        <v>87.379967140000005</v>
+        <v>87.379967135716399</v>
       </c>
       <c r="F23" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="G23">
-        <v>22.690868699999999</v>
+        <v>22.690868695213929</v>
       </c>
       <c r="H23">
-        <v>87.379967140000005</v>
+        <v>87.379967135716399</v>
       </c>
     </row>
     <row r="24" spans="2:8">
@@ -31843,19 +31802,19 @@
         <v>410</v>
       </c>
       <c r="C24">
-        <v>27.511525379999998</v>
+        <v>27.5115253825116</v>
       </c>
       <c r="D24">
-        <v>72.48193594</v>
+        <v>72.481935936664442</v>
       </c>
       <c r="F24" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="G24">
-        <v>27.511525379999998</v>
+        <v>27.5115253825116</v>
       </c>
       <c r="H24">
-        <v>72.48193594</v>
+        <v>72.481935936664442</v>
       </c>
     </row>
     <row r="25" spans="2:8">
@@ -31863,16 +31822,16 @@
         <v>411</v>
       </c>
       <c r="C25">
-        <v>17.159797170000001</v>
+        <v>17.15979717252354</v>
       </c>
       <c r="D25">
         <v>81.895088599999994</v>
       </c>
       <c r="F25" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="G25">
-        <v>17.159797170000001</v>
+        <v>17.15979717252354</v>
       </c>
       <c r="H25">
         <v>81.895088599999994</v>
@@ -31883,19 +31842,19 @@
         <v>412</v>
       </c>
       <c r="C26">
-        <v>26.87410388</v>
+        <v>26.874103883267651</v>
       </c>
       <c r="D26">
-        <v>92.769229429999996</v>
+        <v>92.769229427644319</v>
       </c>
       <c r="F26" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="G26">
-        <v>26.87410388</v>
+        <v>26.874103883267651</v>
       </c>
       <c r="H26">
-        <v>92.769229429999996</v>
+        <v>92.769229427644319</v>
       </c>
     </row>
     <row r="27" spans="2:8">
@@ -31903,19 +31862,19 @@
         <v>413</v>
       </c>
       <c r="C27">
-        <v>23.940177048687382</v>
+        <v>27.893720802676519</v>
       </c>
       <c r="D27">
-        <v>72.01530541613829</v>
+        <v>95.162232610422222</v>
       </c>
       <c r="F27" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="G27">
-        <v>23.940177048687382</v>
+        <v>27.893720802676519</v>
       </c>
       <c r="H27">
-        <v>72.01530541613829</v>
+        <v>95.162232610422222</v>
       </c>
     </row>
     <row r="28" spans="2:8">
@@ -31923,19 +31882,19 @@
         <v>414</v>
       </c>
       <c r="C28">
-        <v>25.762589391573918</v>
+        <v>27.616837641447088</v>
       </c>
       <c r="D28">
-        <v>72.323497564065292</v>
+        <v>95.678904356646044</v>
       </c>
       <c r="F28" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="G28">
-        <v>25.762589391573918</v>
+        <v>27.616837641447088</v>
       </c>
       <c r="H28">
-        <v>72.323497564065292</v>
+        <v>95.678904356646044</v>
       </c>
     </row>
     <row r="29" spans="2:8">
@@ -31943,19 +31902,19 @@
         <v>415</v>
       </c>
       <c r="C29">
-        <v>25.215717246195734</v>
+        <v>27.109313934866226</v>
       </c>
       <c r="D29">
-        <v>74.92863083024271</v>
+        <v>94.597756225167842</v>
       </c>
       <c r="F29" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="G29">
-        <v>25.215717246195734</v>
+        <v>27.109313934866226</v>
       </c>
       <c r="H29">
-        <v>74.92863083024271</v>
+        <v>94.597756225167842</v>
       </c>
     </row>
     <row r="30" spans="2:8">
@@ -31963,19 +31922,19 @@
         <v>416</v>
       </c>
       <c r="C30">
-        <v>22.089771430079018</v>
+        <v>26.973082364209532</v>
       </c>
       <c r="D30">
-        <v>71.979982922841245</v>
+        <v>92.084380653014193</v>
       </c>
       <c r="F30" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="G30">
-        <v>22.089771430079018</v>
+        <v>26.973082364209532</v>
       </c>
       <c r="H30">
-        <v>71.979982922841245</v>
+        <v>92.084380653014193</v>
       </c>
     </row>
     <row r="31" spans="2:8">
@@ -31983,19 +31942,19 @@
         <v>417</v>
       </c>
       <c r="C31">
-        <v>23.401710039230601</v>
+        <v>25.331244673876583</v>
       </c>
       <c r="D31">
-        <v>73.75439597012047</v>
+        <v>90.580571695618644</v>
       </c>
       <c r="F31" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="G31">
-        <v>23.401710039230601</v>
+        <v>25.331244673876583</v>
       </c>
       <c r="H31">
-        <v>73.75439597012047</v>
+        <v>90.580571695618644</v>
       </c>
     </row>
     <row r="32" spans="2:8">
@@ -32003,19 +31962,19 @@
         <v>418</v>
       </c>
       <c r="C32">
-        <v>19.571868623472721</v>
+        <v>26.347320792040019</v>
       </c>
       <c r="D32">
-        <v>73.203935226300871</v>
+        <v>90.088813711116686</v>
       </c>
       <c r="F32" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="G32">
-        <v>19.571868623472721</v>
+        <v>26.347320792040019</v>
       </c>
       <c r="H32">
-        <v>73.203935226300871</v>
+        <v>90.088813711116686</v>
       </c>
     </row>
     <row r="33" spans="2:8">
@@ -32023,19 +31982,19 @@
         <v>419</v>
       </c>
       <c r="C33">
-        <v>20.973992616098737</v>
+        <v>22.65193104025149</v>
       </c>
       <c r="D33">
-        <v>74.655550178307777</v>
+        <v>92.546702607694158</v>
       </c>
       <c r="F33" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="G33">
-        <v>20.973992616098737</v>
+        <v>22.65193104025149</v>
       </c>
       <c r="H33">
-        <v>74.655550178307777</v>
+        <v>92.546702607694158</v>
       </c>
     </row>
     <row r="34" spans="2:8">
@@ -32043,19 +32002,19 @@
         <v>420</v>
       </c>
       <c r="C34">
-        <v>21.298615212019719</v>
+        <v>23.777133025144924</v>
       </c>
       <c r="D34">
-        <v>78.132581760570787</v>
+        <v>91.654903285132121</v>
       </c>
       <c r="F34" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="G34">
-        <v>21.298615212019719</v>
+        <v>23.777133025144924</v>
       </c>
       <c r="H34">
-        <v>78.132581760570787</v>
+        <v>91.654903285132121</v>
       </c>
     </row>
     <row r="35" spans="2:8">
@@ -32063,19 +32022,19 @@
         <v>421</v>
       </c>
       <c r="C35">
-        <v>20.763554465432239</v>
+        <v>26.335074800055896</v>
       </c>
       <c r="D35">
-        <v>76.329011042015125</v>
+        <v>92.986095851336842</v>
       </c>
       <c r="F35" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="G35">
-        <v>20.763554465432239</v>
+        <v>26.335074800055896</v>
       </c>
       <c r="H35">
-        <v>76.329011042015125</v>
+        <v>92.986095851336842</v>
       </c>
     </row>
     <row r="36" spans="2:8">
@@ -32083,19 +32042,19 @@
         <v>422</v>
       </c>
       <c r="C36">
-        <v>23.23600900338716</v>
+        <v>25.924881972559486</v>
       </c>
       <c r="D36">
-        <v>75.739329326526175</v>
+        <v>94.269460528249525</v>
       </c>
       <c r="F36" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="G36">
-        <v>23.23600900338716</v>
+        <v>25.924881972559486</v>
       </c>
       <c r="H36">
-        <v>75.739329326526175</v>
+        <v>94.269460528249525</v>
       </c>
     </row>
     <row r="37" spans="2:8">
@@ -32103,19 +32062,19 @@
         <v>423</v>
       </c>
       <c r="C37">
-        <v>23.441086592996527</v>
+        <v>24.796283713760488</v>
       </c>
       <c r="D37">
-        <v>77.538069578828527</v>
+        <v>92.445894855815595</v>
       </c>
       <c r="F37" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="G37">
-        <v>23.441086592996527</v>
+        <v>24.796283713760488</v>
       </c>
       <c r="H37">
-        <v>77.538069578828527</v>
+        <v>92.445894855815595</v>
       </c>
     </row>
     <row r="38" spans="2:8">
@@ -32123,19 +32082,19 @@
         <v>424</v>
       </c>
       <c r="C38">
-        <v>29.451941382432882</v>
+        <v>24.450646852147571</v>
       </c>
       <c r="D38">
-        <v>73.848509064471259</v>
+        <v>94.345871649004167</v>
       </c>
       <c r="F38" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="G38">
-        <v>29.451941382432882</v>
+        <v>24.450646852147571</v>
       </c>
       <c r="H38">
-        <v>73.848509064471259</v>
+        <v>94.345871649004167</v>
       </c>
     </row>
     <row r="39" spans="2:8">
@@ -32143,19 +32102,19 @@
         <v>425</v>
       </c>
       <c r="C39">
-        <v>30.889610466578063</v>
+        <v>24.31722425770889</v>
       </c>
       <c r="D39">
-        <v>74.994352434716205</v>
+        <v>80.606617981443563</v>
       </c>
       <c r="F39" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="G39">
-        <v>30.889610466578063</v>
+        <v>24.31722425770889</v>
       </c>
       <c r="H39">
-        <v>74.994352434716205</v>
+        <v>80.606617981443563</v>
       </c>
     </row>
     <row r="40" spans="2:8">
@@ -32163,19 +32122,19 @@
         <v>426</v>
       </c>
       <c r="C40">
-        <v>27.782553394318072</v>
+        <v>27.55951580673932</v>
       </c>
       <c r="D40">
-        <v>72.130555374386333</v>
+        <v>81.958507480329203</v>
       </c>
       <c r="F40" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="G40">
-        <v>27.782553394318072</v>
+        <v>27.55951580673932</v>
       </c>
       <c r="H40">
-        <v>72.130555374386333</v>
+        <v>81.958507480329203</v>
       </c>
     </row>
     <row r="41" spans="2:8">
@@ -32183,19 +32142,19 @@
         <v>427</v>
       </c>
       <c r="C41">
-        <v>27.999653865710783</v>
+        <v>26.383501441796746</v>
       </c>
       <c r="D41">
-        <v>74.792171203407761</v>
+        <v>79.699115070602147</v>
       </c>
       <c r="F41" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="G41">
-        <v>27.999653865710783</v>
+        <v>26.383501441796746</v>
       </c>
       <c r="H41">
-        <v>74.792171203407761</v>
+        <v>79.699115070602147</v>
       </c>
     </row>
     <row r="42" spans="2:8">
@@ -32203,19 +32162,19 @@
         <v>428</v>
       </c>
       <c r="C42">
-        <v>32.369004546556781</v>
+        <v>25.961441796472709</v>
       </c>
       <c r="D42">
-        <v>75.328108254891234</v>
+        <v>81.513212233838857</v>
       </c>
       <c r="F42" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="G42">
-        <v>32.369004546556781</v>
+        <v>25.961441796472709</v>
       </c>
       <c r="H42">
-        <v>75.328108254891234</v>
+        <v>81.513212233838857</v>
       </c>
     </row>
     <row r="43" spans="2:8">
@@ -32223,19 +32182,19 @@
         <v>429</v>
       </c>
       <c r="C43">
-        <v>30.078269892451456</v>
+        <v>26.525927540081284</v>
       </c>
       <c r="D43">
-        <v>77.138454353946159</v>
+        <v>84.428490924191877</v>
       </c>
       <c r="F43" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="G43">
-        <v>30.078269892451456</v>
+        <v>26.525927540081284</v>
       </c>
       <c r="H43">
-        <v>77.138454353946159</v>
+        <v>84.428490924191877</v>
       </c>
     </row>
     <row r="44" spans="2:8">
@@ -32243,19 +32202,19 @@
         <v>430</v>
       </c>
       <c r="C44">
-        <v>25.353800245391959</v>
+        <v>24.521017808688651</v>
       </c>
       <c r="D44">
-        <v>77.66979989677975</v>
+        <v>83.582913959798233</v>
       </c>
       <c r="F44" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="G44">
-        <v>25.353800245391959</v>
+        <v>24.521017808688651</v>
       </c>
       <c r="H44">
-        <v>77.66979989677975</v>
+        <v>83.582913959798233</v>
       </c>
     </row>
     <row r="45" spans="2:8">
@@ -32263,19 +32222,19 @@
         <v>431</v>
       </c>
       <c r="C45">
-        <v>24.69495322947316</v>
+        <v>20.267712814945369</v>
       </c>
       <c r="D45">
-        <v>79.922674256012414</v>
+        <v>85.020972700910107</v>
       </c>
       <c r="F45" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="G45">
-        <v>24.69495322947316</v>
+        <v>20.267712814945369</v>
       </c>
       <c r="H45">
-        <v>79.922674256012414</v>
+        <v>85.020972700910107</v>
       </c>
     </row>
     <row r="46" spans="2:8">
@@ -32283,19 +32242,19 @@
         <v>432</v>
       </c>
       <c r="C46">
-        <v>26.471952337563291</v>
+        <v>21.316843980271184</v>
       </c>
       <c r="D46">
-        <v>79.723985175188076</v>
+        <v>86.506425397145236</v>
       </c>
       <c r="F46" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="G46">
-        <v>26.471952337563291</v>
+        <v>21.316843980271184</v>
       </c>
       <c r="H46">
-        <v>79.723985175188076</v>
+        <v>86.506425397145236</v>
       </c>
     </row>
     <row r="47" spans="2:8">
@@ -32303,19 +32262,19 @@
         <v>433</v>
       </c>
       <c r="C47">
-        <v>26.884841613709771</v>
+        <v>21.043761288625959</v>
       </c>
       <c r="D47">
-        <v>76.380230155914333</v>
+        <v>83.399512273884866</v>
       </c>
       <c r="F47" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="G47">
-        <v>26.884841613709771</v>
+        <v>21.043761288625959</v>
       </c>
       <c r="H47">
-        <v>76.380230155914333</v>
+        <v>83.399512273884866</v>
       </c>
     </row>
     <row r="48" spans="2:8">
@@ -32323,19 +32282,19 @@
         <v>434</v>
       </c>
       <c r="C48">
-        <v>28.171500161202225</v>
+        <v>22.301037494716983</v>
       </c>
       <c r="D48">
-        <v>77.457861310026132</v>
+        <v>84.691615831874245</v>
       </c>
       <c r="F48" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="G48">
-        <v>28.171500161202225</v>
+        <v>22.301037494716983</v>
       </c>
       <c r="H48">
-        <v>77.457861310026132</v>
+        <v>84.691615831874245</v>
       </c>
     </row>
     <row r="49" spans="2:8">
@@ -32343,19 +32302,19 @@
         <v>435</v>
       </c>
       <c r="C49">
-        <v>29.347431056795799</v>
+        <v>26.058253347633784</v>
       </c>
       <c r="D49">
-        <v>79.647824868329138</v>
+        <v>87.628239095813171</v>
       </c>
       <c r="F49" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="G49">
-        <v>29.347431056795799</v>
+        <v>26.058253347633784</v>
       </c>
       <c r="H49">
-        <v>79.647824868329138</v>
+        <v>87.628239095813171</v>
       </c>
     </row>
     <row r="50" spans="2:8">
@@ -32363,19 +32322,19 @@
         <v>436</v>
       </c>
       <c r="C50">
-        <v>28.214905273412281</v>
+        <v>23.631935868013976</v>
       </c>
       <c r="D50">
-        <v>79.817174165971352</v>
+        <v>88.065380035257064</v>
       </c>
       <c r="F50" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="G50">
-        <v>28.214905273412281</v>
+        <v>23.631935868013976</v>
       </c>
       <c r="H50">
-        <v>79.817174165971352</v>
+        <v>88.065380035257064</v>
       </c>
     </row>
     <row r="51" spans="2:8">
@@ -32383,19 +32342,19 @@
         <v>437</v>
       </c>
       <c r="C51">
-        <v>26.542230132073865</v>
+        <v>24.80613255949843</v>
       </c>
       <c r="D51">
-        <v>84.906854690618076</v>
+        <v>87.744335886089701</v>
       </c>
       <c r="F51" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="G51">
-        <v>26.542230132073865</v>
+        <v>24.80613255949843</v>
       </c>
       <c r="H51">
-        <v>84.906854690618076</v>
+        <v>87.744335886089701</v>
       </c>
     </row>
     <row r="52" spans="2:8">
@@ -32403,19 +32362,19 @@
         <v>438</v>
       </c>
       <c r="C52">
-        <v>27.41535306419388</v>
+        <v>22.45842969369151</v>
       </c>
       <c r="D52">
-        <v>81.909913684164707</v>
+        <v>88.438189470207149</v>
       </c>
       <c r="F52" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="G52">
-        <v>27.41535306419388</v>
+        <v>22.45842969369151</v>
       </c>
       <c r="H52">
-        <v>81.909913684164707</v>
+        <v>88.438189470207149</v>
       </c>
     </row>
     <row r="53" spans="2:8">
@@ -32423,19 +32382,19 @@
         <v>439</v>
       </c>
       <c r="C53">
-        <v>24.931943564621783</v>
+        <v>22.927728025420791</v>
       </c>
       <c r="D53">
-        <v>82.064463522199645</v>
+        <v>86.722505798487134</v>
       </c>
       <c r="F53" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="G53">
-        <v>24.931943564621783</v>
+        <v>22.927728025420791</v>
       </c>
       <c r="H53">
-        <v>82.064463522199645</v>
+        <v>86.722505798487134</v>
       </c>
     </row>
     <row r="54" spans="2:8">
@@ -32443,19 +32402,19 @@
         <v>440</v>
       </c>
       <c r="C54">
-        <v>25.570037966723085</v>
+        <v>24.187657520268608</v>
       </c>
       <c r="D54">
-        <v>83.663810272051307</v>
+        <v>85.735856534484711</v>
       </c>
       <c r="F54" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="G54">
-        <v>25.570037966723085</v>
+        <v>24.187657520268608</v>
       </c>
       <c r="H54">
-        <v>83.663810272051307</v>
+        <v>85.735856534484711</v>
       </c>
     </row>
     <row r="55" spans="2:8">
@@ -32463,19 +32422,19 @@
         <v>441</v>
       </c>
       <c r="C55">
-        <v>26.822004333517569</v>
+        <v>10.504393335127451</v>
       </c>
       <c r="D55">
-        <v>70.209932684848098</v>
+        <v>78.878413559497417</v>
       </c>
       <c r="F55" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="G55">
-        <v>26.822004333517569</v>
+        <v>10.504393335127451</v>
       </c>
       <c r="H55">
-        <v>70.209932684848098</v>
+        <v>78.878413559497417</v>
       </c>
     </row>
     <row r="56" spans="2:8">
@@ -32483,19 +32442,19 @@
         <v>442</v>
       </c>
       <c r="C56">
-        <v>23.974943881323178</v>
+        <v>9.137397690734506</v>
       </c>
       <c r="D56">
-        <v>69.9628674302528</v>
+        <v>77.06767511606877</v>
       </c>
       <c r="F56" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="G56">
-        <v>23.974943881323178</v>
+        <v>9.137397690734506</v>
       </c>
       <c r="H56">
-        <v>69.9628674302528</v>
+        <v>77.06767511606877</v>
       </c>
     </row>
     <row r="57" spans="2:8">
@@ -32503,19 +32462,19 @@
         <v>443</v>
       </c>
       <c r="C57">
-        <v>22.031083021744013</v>
+        <v>11.226969498165088</v>
       </c>
       <c r="D57">
-        <v>70.312870487012432</v>
+        <v>76.558554080404249</v>
       </c>
       <c r="F57" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="G57">
-        <v>22.031083021744013</v>
+        <v>11.226969498165088</v>
       </c>
       <c r="H57">
-        <v>70.312870487012432</v>
+        <v>76.558554080404249</v>
       </c>
     </row>
     <row r="58" spans="2:8">
@@ -32523,19 +32482,19 @@
         <v>444</v>
       </c>
       <c r="C58">
-        <v>22.183640582672592</v>
+        <v>11.507621226853775</v>
       </c>
       <c r="D58">
-        <v>87.63284952501175</v>
+        <v>78.030451964254922</v>
       </c>
       <c r="F58" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="G58">
-        <v>22.183640582672592</v>
+        <v>11.507621226853775</v>
       </c>
       <c r="H58">
-        <v>87.63284952501175</v>
+        <v>78.030451964254922</v>
       </c>
     </row>
     <row r="59" spans="2:8">
@@ -32543,19 +32502,19 @@
         <v>445</v>
       </c>
       <c r="C59">
-        <v>25.988701451121266</v>
+        <v>18.297166863653832</v>
       </c>
       <c r="D59">
-        <v>87.799415974822153</v>
+        <v>83.515249081931756</v>
       </c>
       <c r="F59" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="G59">
-        <v>25.988701451121266</v>
+        <v>18.297166863653832</v>
       </c>
       <c r="H59">
-        <v>87.799415974822153</v>
+        <v>83.515249081931756</v>
       </c>
     </row>
     <row r="60" spans="2:8">
@@ -32563,19 +32522,19 @@
         <v>446</v>
       </c>
       <c r="C60">
-        <v>24.75124696562656</v>
+        <v>16.746787868199885</v>
       </c>
       <c r="D60">
-        <v>87.749394240479006</v>
+        <v>80.766065933161698</v>
       </c>
       <c r="F60" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="G60">
-        <v>24.75124696562656</v>
+        <v>16.746787868199885</v>
       </c>
       <c r="H60">
-        <v>87.749394240479006</v>
+        <v>80.766065933161698</v>
       </c>
     </row>
     <row r="61" spans="2:8">
@@ -32583,19 +32542,19 @@
         <v>447</v>
       </c>
       <c r="C61">
-        <v>23.593158281395816</v>
+        <v>16.717737568197382</v>
       </c>
       <c r="D61">
-        <v>87.503087921397949</v>
+        <v>77.592607797183973</v>
       </c>
       <c r="F61" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="G61">
-        <v>23.593158281395816</v>
+        <v>16.717737568197382</v>
       </c>
       <c r="H61">
-        <v>87.503087921397949</v>
+        <v>77.592607797183973</v>
       </c>
     </row>
     <row r="62" spans="2:8">
@@ -32603,19 +32562,19 @@
         <v>448</v>
       </c>
       <c r="C62">
-        <v>24.450646852147571</v>
+        <v>15.655512883330466</v>
       </c>
       <c r="D62">
-        <v>94.345871649004167</v>
+        <v>78.53671045262692</v>
       </c>
       <c r="F62" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="G62">
-        <v>24.450646852147571</v>
+        <v>15.655512883330466</v>
       </c>
       <c r="H62">
-        <v>94.345871649004167</v>
+        <v>78.53671045262692</v>
       </c>
     </row>
     <row r="63" spans="2:8">
@@ -32623,19 +32582,19 @@
         <v>449</v>
       </c>
       <c r="C63">
-        <v>25.932079217995447</v>
+        <v>12.695725765835803</v>
       </c>
       <c r="D63">
-        <v>94.275813463711927</v>
+        <v>79.600537241704529</v>
       </c>
       <c r="F63" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="G63">
-        <v>25.932079217995447</v>
+        <v>12.695725765835803</v>
       </c>
       <c r="H63">
-        <v>94.275813463711927</v>
+        <v>79.600537241704529</v>
       </c>
     </row>
     <row r="64" spans="2:8">
@@ -32643,19 +32602,19 @@
         <v>450</v>
       </c>
       <c r="C64">
-        <v>25.370723287781249</v>
+        <v>14.595490354840878</v>
       </c>
       <c r="D64">
-        <v>92.647721575694646</v>
+        <v>79.645710453009926</v>
       </c>
       <c r="F64" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="G64">
-        <v>25.370723287781249</v>
+        <v>14.595490354840878</v>
       </c>
       <c r="H64">
-        <v>92.647721575694646</v>
+        <v>79.645710453009926</v>
       </c>
     </row>
     <row r="65" spans="2:8">
@@ -32663,19 +32622,19 @@
         <v>451</v>
       </c>
       <c r="C65">
-        <v>22.573062394491476</v>
+        <v>13.73915763611522</v>
       </c>
       <c r="D65">
-        <v>92.547734691435167</v>
+        <v>78.335810324430909</v>
       </c>
       <c r="F65" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="G65">
-        <v>22.573062394491476</v>
+        <v>13.73915763611522</v>
       </c>
       <c r="H65">
-        <v>92.547734691435167</v>
+        <v>78.335810324430909</v>
       </c>
     </row>
     <row r="66" spans="2:8">
@@ -32683,19 +32642,19 @@
         <v>452</v>
       </c>
       <c r="C66">
-        <v>23.77438784675067</v>
+        <v>19.119778400148171</v>
       </c>
       <c r="D66">
-        <v>91.660951031916625</v>
+        <v>74.876957067998788</v>
       </c>
       <c r="F66" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="G66">
-        <v>23.77438784675067</v>
+        <v>19.119778400148171</v>
       </c>
       <c r="H66">
-        <v>91.660951031916625</v>
+        <v>74.876957067998788</v>
       </c>
     </row>
     <row r="67" spans="2:8">
@@ -32703,19 +32662,19 @@
         <v>453</v>
       </c>
       <c r="C67">
-        <v>26.855882172919969</v>
+        <v>18.07393392476046</v>
       </c>
       <c r="D67">
-        <v>93.709478990781804</v>
+        <v>73.5913244181788</v>
       </c>
       <c r="F67" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="G67">
-        <v>26.855882172919969</v>
+        <v>18.07393392476046</v>
       </c>
       <c r="H67">
-        <v>93.709478990781804</v>
+        <v>73.5913244181788</v>
       </c>
     </row>
     <row r="68" spans="2:8">
@@ -32723,19 +32682,19 @@
         <v>454</v>
       </c>
       <c r="C68">
-        <v>27.576626654773627</v>
+        <v>18.656031955819039</v>
       </c>
       <c r="D68">
-        <v>95.65235899806126</v>
+        <v>77.156379009071188</v>
       </c>
       <c r="F68" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="G68">
-        <v>27.576626654773627</v>
+        <v>18.656031955819039</v>
       </c>
       <c r="H68">
-        <v>95.65235899806126</v>
+        <v>77.156379009071188</v>
       </c>
     </row>
     <row r="69" spans="2:8">
@@ -32743,19 +32702,19 @@
         <v>455</v>
       </c>
       <c r="C69">
-        <v>27.94126922135878</v>
+        <v>17.568426359523951</v>
       </c>
       <c r="D69">
-        <v>95.290401439517126</v>
+        <v>75.487933132067681</v>
       </c>
       <c r="F69" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="G69">
-        <v>27.94126922135878</v>
+        <v>17.568426359523951</v>
       </c>
       <c r="H69">
-        <v>95.290401439517126</v>
+        <v>75.487933132067681</v>
       </c>
     </row>
     <row r="70" spans="2:8">
@@ -32763,19 +32722,19 @@
         <v>456</v>
       </c>
       <c r="C70">
-        <v>25.715655993691403</v>
+        <v>15.702788983402606</v>
       </c>
       <c r="D70">
-        <v>90.488191424015938</v>
+        <v>74.542637644301038</v>
       </c>
       <c r="F70" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="G70">
-        <v>25.715655993691403</v>
+        <v>15.702788983402606</v>
       </c>
       <c r="H70">
-        <v>90.488191424015938</v>
+        <v>74.542637644301038</v>
       </c>
     </row>
     <row r="71" spans="2:8">
@@ -32783,19 +32742,19 @@
         <v>457</v>
       </c>
       <c r="C71">
-        <v>26.580928877190129</v>
+        <v>15.54304126688014</v>
       </c>
       <c r="D71">
-        <v>88.899556417890167</v>
+        <v>75.8502505173728</v>
       </c>
       <c r="F71" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="G71">
-        <v>26.580928877190129</v>
+        <v>15.54304126688014</v>
       </c>
       <c r="H71">
-        <v>88.899556417890167</v>
+        <v>75.8502505173728</v>
       </c>
     </row>
     <row r="72" spans="2:8">
@@ -32803,19 +32762,19 @@
         <v>458</v>
       </c>
       <c r="C72">
-        <v>26.58118329802992</v>
+        <v>13.2686602697427</v>
       </c>
       <c r="D72">
-        <v>90.902380510161123</v>
+        <v>76.682358237502683</v>
       </c>
       <c r="F72" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="G72">
-        <v>26.58118329802992</v>
+        <v>13.2686602697427</v>
       </c>
       <c r="H72">
-        <v>90.902380510161123</v>
+        <v>76.682358237502683</v>
       </c>
     </row>
     <row r="73" spans="2:8">
@@ -32823,19 +32782,19 @@
         <v>459</v>
       </c>
       <c r="C73">
-        <v>18.504131255890169</v>
+        <v>13.284216758700872</v>
       </c>
       <c r="D73">
-        <v>83.874432570520142</v>
+        <v>75.227500296397494</v>
       </c>
       <c r="F73" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="G73">
-        <v>18.504131255890169</v>
+        <v>13.284216758700872</v>
       </c>
       <c r="H73">
-        <v>83.874432570520142</v>
+        <v>75.227500296397494</v>
       </c>
     </row>
     <row r="74" spans="2:8">
@@ -32843,19 +32802,19 @@
         <v>460</v>
       </c>
       <c r="C74">
-        <v>20.089138134163729</v>
+        <v>21.853538373607162</v>
       </c>
       <c r="D74">
-        <v>85.185447365975165</v>
+        <v>79.484349098731869</v>
       </c>
       <c r="F74" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="G74">
-        <v>20.089138134163729</v>
+        <v>21.853538373607162</v>
       </c>
       <c r="H74">
-        <v>85.185447365975165</v>
+        <v>79.484349098731869</v>
       </c>
     </row>
     <row r="75" spans="2:8">
@@ -32863,19 +32822,19 @@
         <v>461</v>
       </c>
       <c r="C75">
-        <v>18.857584565270912</v>
+        <v>22.884527788344801</v>
       </c>
       <c r="D75">
-        <v>80.447788094688121</v>
+        <v>81.738794488667125</v>
       </c>
       <c r="F75" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="G75">
-        <v>18.857584565270912</v>
+        <v>22.884527788344801</v>
       </c>
       <c r="H75">
-        <v>80.447788094688121</v>
+        <v>81.738794488667125</v>
       </c>
     </row>
     <row r="76" spans="2:8">
@@ -32883,19 +32842,19 @@
         <v>462</v>
       </c>
       <c r="C76">
-        <v>18.661158935770491</v>
+        <v>21.505424226989053</v>
       </c>
       <c r="D76">
-        <v>82.131914309855873</v>
+        <v>81.78926268910061</v>
       </c>
       <c r="F76" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="G76">
-        <v>18.661158935770491</v>
+        <v>21.505424226989053</v>
       </c>
       <c r="H76">
-        <v>82.131914309855873</v>
+        <v>81.78926268910061</v>
       </c>
     </row>
     <row r="77" spans="2:8">
@@ -32903,19 +32862,19 @@
         <v>463</v>
       </c>
       <c r="C77">
-        <v>19.901684051495504</v>
+        <v>18.616083753584618</v>
       </c>
       <c r="D77">
-        <v>82.249640216459966</v>
+        <v>82.163640057751238</v>
       </c>
       <c r="F77" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="G77">
-        <v>19.901684051495504</v>
+        <v>18.616083753584618</v>
       </c>
       <c r="H77">
-        <v>82.249640216459966</v>
+        <v>82.163640057751238</v>
       </c>
     </row>
     <row r="78" spans="2:8">
@@ -32923,19 +32882,19 @@
         <v>464</v>
       </c>
       <c r="C78">
-        <v>22.705224286477208</v>
+        <v>19.532993714286292</v>
       </c>
       <c r="D78">
-        <v>80.212365572123872</v>
+        <v>81.480874680905245</v>
       </c>
       <c r="F78" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="G78">
-        <v>22.705224286477208</v>
+        <v>19.532993714286292</v>
       </c>
       <c r="H78">
-        <v>80.212365572123872</v>
+        <v>81.480874680905245</v>
       </c>
     </row>
     <row r="79" spans="2:8">
@@ -32943,19 +32902,19 @@
         <v>465</v>
       </c>
       <c r="C79">
-        <v>20.394113196239889</v>
+        <v>19.865313903785481</v>
       </c>
       <c r="D79">
-        <v>79.947473267587768</v>
+        <v>79.14195624358581</v>
       </c>
       <c r="F79" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="G79">
-        <v>20.394113196239889</v>
+        <v>19.865313903785481</v>
       </c>
       <c r="H79">
-        <v>79.947473267587768</v>
+        <v>79.14195624358581</v>
       </c>
     </row>
     <row r="80" spans="2:8">
@@ -32963,19 +32922,19 @@
         <v>466</v>
       </c>
       <c r="C80">
-        <v>21.386323508456584</v>
+        <v>18.192057864555959</v>
       </c>
       <c r="D80">
-        <v>81.554009768177181</v>
+        <v>79.717592517095639</v>
       </c>
       <c r="F80" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="G80">
-        <v>21.386323508456584</v>
+        <v>18.192057864555959</v>
       </c>
       <c r="H80">
-        <v>81.554009768177181</v>
+        <v>79.717592517095639</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -32983,19 +32942,19 @@
         <v>467</v>
       </c>
       <c r="C81">
-        <v>21.45494863014677</v>
+        <v>25.212889640967767</v>
       </c>
       <c r="D81">
-        <v>83.489328677981362</v>
+        <v>73.964019938268009</v>
       </c>
       <c r="F81" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="G81">
-        <v>21.45494863014677</v>
+        <v>25.212889640967767</v>
       </c>
       <c r="H81">
-        <v>83.489328677981362</v>
+        <v>73.964019938268009</v>
       </c>
     </row>
     <row r="82" spans="2:8">
@@ -33003,19 +32962,19 @@
         <v>468</v>
       </c>
       <c r="C82">
-        <v>22.18323596791473</v>
+        <v>21.690024624190663</v>
       </c>
       <c r="D82">
-        <v>85.583788240668881</v>
+        <v>71.764037802011089</v>
       </c>
       <c r="F82" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="G82">
-        <v>22.18323596791473</v>
+        <v>21.690024624190663</v>
       </c>
       <c r="H82">
-        <v>85.583788240668881</v>
+        <v>71.764037802011089</v>
       </c>
     </row>
     <row r="83" spans="2:8">
@@ -33023,19 +32982,19 @@
         <v>469</v>
       </c>
       <c r="C83">
-        <v>23.057557657357972</v>
+        <v>22.939448631127931</v>
       </c>
       <c r="D83">
-        <v>82.955875010904052</v>
+        <v>71.335782385461201</v>
       </c>
       <c r="F83" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="G83">
-        <v>23.057557657357972</v>
+        <v>22.939448631127931</v>
       </c>
       <c r="H83">
-        <v>82.955875010904052</v>
+        <v>71.335782385461201</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -33043,19 +33002,19 @@
         <v>470</v>
       </c>
       <c r="C84">
-        <v>24.189709830493399</v>
+        <v>25.528712199645032</v>
       </c>
       <c r="D84">
-        <v>85.043593089105116</v>
+        <v>71.914824943781099</v>
       </c>
       <c r="F84" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="G84">
-        <v>24.189709830493399</v>
+        <v>25.528712199645032</v>
       </c>
       <c r="H84">
-        <v>85.043593089105116</v>
+        <v>71.914824943781099</v>
       </c>
     </row>
     <row r="85" spans="2:8">
@@ -33063,19 +33022,19 @@
         <v>471</v>
       </c>
       <c r="C85">
-        <v>17.165250319183521</v>
+        <v>23.580064059585681</v>
       </c>
       <c r="D85">
-        <v>76.927061367471381</v>
+        <v>69.641559139694749</v>
       </c>
       <c r="F85" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="G85">
-        <v>17.165250319183521</v>
+        <v>23.580064059585681</v>
       </c>
       <c r="H85">
-        <v>76.927061367471381</v>
+        <v>69.641559139694749</v>
       </c>
     </row>
     <row r="86" spans="2:8">
@@ -33083,19 +33042,19 @@
         <v>472</v>
       </c>
       <c r="C86">
-        <v>18.682280085562315</v>
+        <v>20.220733501265094</v>
       </c>
       <c r="D86">
-        <v>78.467237584757981</v>
+        <v>76.2529578606689</v>
       </c>
       <c r="F86" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="G86">
-        <v>18.682280085562315</v>
+        <v>20.220733501265094</v>
       </c>
       <c r="H86">
-        <v>78.467237584757981</v>
+        <v>76.2529578606689</v>
       </c>
     </row>
     <row r="87" spans="2:8">
@@ -33103,19 +33062,19 @@
         <v>473</v>
       </c>
       <c r="C87">
-        <v>19.636785620416653</v>
+        <v>21.440879518105877</v>
       </c>
       <c r="D87">
-        <v>77.508765165174864</v>
+        <v>77.468039254618546</v>
       </c>
       <c r="F87" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="G87">
-        <v>19.636785620416653</v>
+        <v>21.440879518105877</v>
       </c>
       <c r="H87">
-        <v>77.508765165174864</v>
+        <v>77.468039254618546</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -33123,19 +33082,19 @@
         <v>474</v>
       </c>
       <c r="C88">
-        <v>18.262746739567483</v>
+        <v>20.396478800724161</v>
       </c>
       <c r="D88">
-        <v>75.003230952348488</v>
+        <v>73.197801279068585</v>
       </c>
       <c r="F88" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="G88">
-        <v>18.262746739567483</v>
+        <v>20.396478800724161</v>
       </c>
       <c r="H88">
-        <v>75.003230952348488</v>
+        <v>73.197801279068585</v>
       </c>
     </row>
     <row r="89" spans="2:8">
@@ -33143,19 +33102,19 @@
         <v>475</v>
       </c>
       <c r="C89">
-        <v>15.934631582549706</v>
+        <v>21.259902744576475</v>
       </c>
       <c r="D89">
-        <v>74.177108940575778</v>
+        <v>74.718501437117752</v>
       </c>
       <c r="F89" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="G89">
-        <v>15.934631582549706</v>
+        <v>21.259902744576475</v>
       </c>
       <c r="H89">
-        <v>74.177108940575778</v>
+        <v>74.718501437117752</v>
       </c>
     </row>
     <row r="90" spans="2:8">
@@ -33163,19 +33122,19 @@
         <v>476</v>
       </c>
       <c r="C90">
-        <v>15.564279067442708</v>
+        <v>23.236301590418776</v>
       </c>
       <c r="D90">
-        <v>75.539380148153072</v>
+        <v>73.988713104139038</v>
       </c>
       <c r="F90" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="G90">
-        <v>15.564279067442708</v>
+        <v>23.236301590418776</v>
       </c>
       <c r="H90">
-        <v>75.539380148153072</v>
+        <v>73.988713104139038</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -33183,19 +33142,19 @@
         <v>477</v>
       </c>
       <c r="C91">
-        <v>16.804687119123308</v>
+        <v>23.021647928284843</v>
       </c>
       <c r="D91">
-        <v>81.594689869695102</v>
+        <v>76.360488664096508</v>
       </c>
       <c r="F91" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="G91">
-        <v>16.804687119123308</v>
+        <v>23.021647928284843</v>
       </c>
       <c r="H91">
-        <v>81.594689869695102</v>
+        <v>76.360488664096508</v>
       </c>
     </row>
     <row r="92" spans="2:8">
@@ -33203,19 +33162,19 @@
         <v>478</v>
       </c>
       <c r="C92">
-        <v>17.279361538540549</v>
+        <v>23.844650435637025</v>
       </c>
       <c r="D92">
-        <v>80.199256007373833</v>
+        <v>78.562314318711572</v>
       </c>
       <c r="F92" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="G92">
-        <v>17.279361538540549</v>
+        <v>23.844650435637025</v>
       </c>
       <c r="H92">
-        <v>80.199256007373833</v>
+        <v>78.562314318711572</v>
       </c>
     </row>
     <row r="93" spans="2:8">
@@ -33223,19 +33182,19 @@
         <v>479</v>
       </c>
       <c r="C93">
-        <v>14.083502680353268</v>
+        <v>25.504371809022757</v>
       </c>
       <c r="D93">
-        <v>78.066053560719922</v>
+        <v>78.027034101805441</v>
       </c>
       <c r="F93" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="G93">
-        <v>14.083502680353268</v>
+        <v>25.504371809022757</v>
       </c>
       <c r="H93">
-        <v>78.066053560719922</v>
+        <v>78.027034101805441</v>
       </c>
     </row>
     <row r="94" spans="2:8">
@@ -33243,19 +33202,19 @@
         <v>480</v>
       </c>
       <c r="C94">
-        <v>15.863949455046912</v>
+        <v>24.816296140449264</v>
       </c>
       <c r="D94">
-        <v>78.210973456285771</v>
+        <v>76.434449242765709</v>
       </c>
       <c r="F94" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="G94">
-        <v>15.863949455046912</v>
+        <v>24.816296140449264</v>
       </c>
       <c r="H94">
-        <v>78.210973456285771</v>
+        <v>76.434449242765709</v>
       </c>
     </row>
     <row r="95" spans="2:8">
@@ -33263,19 +33222,19 @@
         <v>481</v>
       </c>
       <c r="C95">
-        <v>12.66263811234435</v>
+        <v>29.40190299120264</v>
       </c>
       <c r="D95">
-        <v>79.339421919695269</v>
+        <v>78.670396495142271</v>
       </c>
       <c r="F95" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="G95">
-        <v>12.66263811234435</v>
+        <v>29.40190299120264</v>
       </c>
       <c r="H95">
-        <v>79.339421919695269</v>
+        <v>78.670396495142271</v>
       </c>
     </row>
     <row r="96" spans="2:8">
@@ -33283,19 +33242,19 @@
         <v>482</v>
       </c>
       <c r="C96">
-        <v>14.622153496205565</v>
+        <v>28.385614913322083</v>
       </c>
       <c r="D96">
-        <v>79.595087805605004</v>
+        <v>79.844150203644304</v>
       </c>
       <c r="F96" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="G96">
-        <v>14.622153496205565</v>
+        <v>28.385614913322083</v>
       </c>
       <c r="H96">
-        <v>79.595087805605004</v>
+        <v>79.844150203644304</v>
       </c>
     </row>
     <row r="97" spans="2:8">
@@ -33303,19 +33262,19 @@
         <v>483</v>
       </c>
       <c r="C97">
-        <v>9.2828165306186659</v>
+        <v>27.882415320274731</v>
       </c>
       <c r="D97">
-        <v>78.456689326362721</v>
+        <v>77.628395787297492</v>
       </c>
       <c r="F97" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="G97">
-        <v>9.2828165306186659</v>
+        <v>27.882415320274731</v>
       </c>
       <c r="H97">
-        <v>78.456689326362721</v>
+        <v>77.628395787297492</v>
       </c>
     </row>
     <row r="98" spans="2:8">
@@ -33323,19 +33282,19 @@
         <v>484</v>
       </c>
       <c r="C98">
-        <v>10.91886508463346</v>
+        <v>26.651001883724671</v>
       </c>
       <c r="D98">
-        <v>79.322415400123347</v>
+        <v>76.124134535246441</v>
       </c>
       <c r="F98" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="G98">
-        <v>10.91886508463346</v>
+        <v>26.651001883724671</v>
       </c>
       <c r="H98">
-        <v>79.322415400123347</v>
+        <v>76.124134535246441</v>
       </c>
     </row>
     <row r="99" spans="2:8">
@@ -33343,19 +33302,19 @@
         <v>485</v>
       </c>
       <c r="C99">
-        <v>10.694962484380181</v>
+        <v>28.185100700140872</v>
       </c>
       <c r="D99">
-        <v>78.22469868970876</v>
+        <v>75.322492960532301</v>
       </c>
       <c r="F99" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="G99">
-        <v>10.694962484380181</v>
+        <v>28.185100700140872</v>
       </c>
       <c r="H99">
-        <v>78.22469868970876</v>
+        <v>75.322492960532301</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -33363,19 +33322,19 @@
         <v>486</v>
       </c>
       <c r="C100">
-        <v>11.070325439391326</v>
+        <v>28.495583704687725</v>
       </c>
       <c r="D100">
-        <v>76.157836475227754</v>
+        <v>73.365935679815195</v>
       </c>
       <c r="F100" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="G100">
-        <v>11.070325439391326</v>
+        <v>28.495583704687725</v>
       </c>
       <c r="H100">
-        <v>76.157836475227754</v>
+        <v>73.365935679815195</v>
       </c>
     </row>
     <row r="101" spans="2:8">
@@ -33383,19 +33342,19 @@
         <v>487</v>
       </c>
       <c r="C101">
-        <v>9.3619369199647302</v>
+        <v>26.892312386477112</v>
       </c>
       <c r="D101">
-        <v>76.933313582397204</v>
+        <v>70.676366152806125</v>
       </c>
       <c r="F101" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="G101">
-        <v>9.3619369199647302</v>
+        <v>26.892312386477112</v>
       </c>
       <c r="H101">
-        <v>76.933313582397204</v>
+        <v>70.676366152806125</v>
       </c>
     </row>
     <row r="102" spans="2:8">
@@ -33403,19 +33362,19 @@
         <v>488</v>
       </c>
       <c r="C102">
-        <v>13.275262016710732</v>
+        <v>30.560929455971198</v>
       </c>
       <c r="D102">
-        <v>75.118441418466219</v>
+        <v>74.979861298391867</v>
       </c>
       <c r="F102" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="G102">
-        <v>13.275262016710732</v>
+        <v>30.560929455971198</v>
       </c>
       <c r="H102">
-        <v>75.118441418466219</v>
+        <v>74.979861298391867</v>
       </c>
     </row>
     <row r="103" spans="2:8">
@@ -33423,19 +33382,19 @@
         <v>489</v>
       </c>
       <c r="C103">
-        <v>12.076302892032931</v>
+        <v>32.369004546556781</v>
       </c>
       <c r="D103">
-        <v>77.39317984021622</v>
+        <v>75.328108254891234</v>
       </c>
       <c r="F103" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="G103">
-        <v>12.076302892032931</v>
+        <v>32.369004546556781</v>
       </c>
       <c r="H103">
-        <v>77.39317984021622</v>
+        <v>75.328108254891234</v>
       </c>
     </row>
     <row r="104" spans="2:8">
@@ -33443,19 +33402,19 @@
         <v>490</v>
       </c>
       <c r="C104">
-        <v>13.183651147633009</v>
+        <v>30.530795340527071</v>
       </c>
       <c r="D104">
-        <v>76.529851619102828</v>
+        <v>77.086231517473834</v>
       </c>
       <c r="F104" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="G104">
-        <v>13.183651147633009</v>
+        <v>30.530795340527071</v>
       </c>
       <c r="H104">
-        <v>76.529851619102828</v>
+        <v>77.086231517473834</v>
       </c>
     </row>
     <row r="105" spans="2:8">
@@ -33463,19 +33422,19 @@
         <v>491</v>
       </c>
       <c r="C105">
-        <v>27.568646248158934</v>
+        <v>21.10302119312308</v>
       </c>
       <c r="D105">
-        <v>80.530279009447071</v>
+        <v>81.836685291033888</v>
       </c>
       <c r="F105" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="G105">
-        <v>27.568646248158934</v>
+        <v>21.10302119312308</v>
       </c>
       <c r="H105">
-        <v>80.530279009447071</v>
+        <v>81.836685291033888</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -33483,19 +33442,19 @@
         <v>492</v>
       </c>
       <c r="C106">
-        <v>27.145978538045068</v>
+        <v>20.564145975997764</v>
       </c>
       <c r="D106">
-        <v>82.691638318475043</v>
+        <v>80.882423042649279</v>
       </c>
       <c r="F106" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="G106">
-        <v>27.145978538045068</v>
+        <v>20.564145975997764</v>
       </c>
       <c r="H106">
-        <v>82.691638318475043</v>
+        <v>80.882423042649279</v>
       </c>
     </row>
     <row r="107" spans="2:8">
@@ -33503,19 +33462,19 @@
         <v>493</v>
       </c>
       <c r="C107">
-        <v>26.261782828491764</v>
+        <v>21.398204141725973</v>
       </c>
       <c r="D107">
-        <v>81.894536080706928</v>
+        <v>78.372555299819496</v>
       </c>
       <c r="F107" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G107">
-        <v>26.261782828491764</v>
+        <v>21.398204141725973</v>
       </c>
       <c r="H107">
-        <v>81.894536080706928</v>
+        <v>78.372555299819496</v>
       </c>
     </row>
     <row r="108" spans="2:8">
@@ -33523,19 +33482,19 @@
         <v>494</v>
       </c>
       <c r="C108">
-        <v>28.793343383966917</v>
+        <v>22.35706706178409</v>
       </c>
       <c r="D108">
-        <v>78.594686526388912</v>
+        <v>79.409394755798345</v>
       </c>
       <c r="F108" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="G108">
-        <v>28.793343383966917</v>
+        <v>22.35706706178409</v>
       </c>
       <c r="H108">
-        <v>78.594686526388912</v>
+        <v>79.409394755798345</v>
       </c>
     </row>
     <row r="109" spans="2:8">
@@ -33543,19 +33502,19 @@
         <v>495</v>
       </c>
       <c r="C109">
-        <v>29.984016069110275</v>
+        <v>17.047156637410964</v>
       </c>
       <c r="D109">
-        <v>76.91112272158604</v>
+        <v>82.080754959948678</v>
       </c>
       <c r="F109" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="G109">
-        <v>29.984016069110275</v>
+        <v>17.047156637410964</v>
       </c>
       <c r="H109">
-        <v>76.91112272158604</v>
+        <v>82.080754959948678</v>
       </c>
     </row>
     <row r="110" spans="2:8">
@@ -33563,19 +33522,19 @@
         <v>496</v>
       </c>
       <c r="C110">
-        <v>27.08812509039273</v>
+        <v>16.542337853473501</v>
       </c>
       <c r="D110">
-        <v>79.18419934082182</v>
+        <v>80.399560371503512</v>
       </c>
       <c r="F110" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G110">
-        <v>27.08812509039273</v>
+        <v>16.542337853473501</v>
       </c>
       <c r="H110">
-        <v>79.18419934082182</v>
+        <v>80.399560371503512</v>
       </c>
     </row>
     <row r="111" spans="2:8">
@@ -33583,19 +33542,19 @@
         <v>497</v>
       </c>
       <c r="C111">
-        <v>26.91880842422681</v>
+        <v>17.900431830287829</v>
       </c>
       <c r="D111">
-        <v>78.186541293088169</v>
+        <v>79.974506488817923</v>
       </c>
       <c r="F111" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="G111">
-        <v>26.91880842422681</v>
+        <v>17.900431830287829</v>
       </c>
       <c r="H111">
-        <v>78.186541293088169</v>
+        <v>79.974506488817923</v>
       </c>
     </row>
     <row r="112" spans="2:8">
@@ -33603,19 +33562,19 @@
         <v>498</v>
       </c>
       <c r="C112">
-        <v>28.675336697419748</v>
+        <v>19.170938202533385</v>
       </c>
       <c r="D112">
-        <v>77.206378475969643</v>
+        <v>82.431444704649735</v>
       </c>
       <c r="F112" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="G112">
-        <v>28.675336697419748</v>
+        <v>19.170938202533385</v>
       </c>
       <c r="H112">
-        <v>77.206378475969643</v>
+        <v>82.431444704649735</v>
       </c>
     </row>
     <row r="113" spans="2:8">
@@ -33623,19 +33582,19 @@
         <v>499</v>
       </c>
       <c r="C113">
-        <v>23.74652281159376</v>
+        <v>19.722675533708053</v>
       </c>
       <c r="D113">
-        <v>80.311440502453877</v>
+        <v>77.850993062754938</v>
       </c>
       <c r="F113" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="G113">
-        <v>23.74652281159376</v>
+        <v>19.722675533708053</v>
       </c>
       <c r="H113">
-        <v>80.311440502453877</v>
+        <v>77.850993062754938</v>
       </c>
     </row>
     <row r="114" spans="2:8">
@@ -33643,19 +33602,19 @@
         <v>500</v>
       </c>
       <c r="C114">
-        <v>23.069873841603343</v>
+        <v>19.634603963339028</v>
       </c>
       <c r="D114">
-        <v>81.66199114710119</v>
+        <v>79.543664029918432</v>
       </c>
       <c r="F114" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="G114">
-        <v>23.069873841603343</v>
+        <v>19.634603963339028</v>
       </c>
       <c r="H114">
-        <v>81.66199114710119</v>
+        <v>79.543664029918432</v>
       </c>
     </row>
     <row r="115" spans="2:8">
@@ -33663,19 +33622,19 @@
         <v>501</v>
       </c>
       <c r="C115">
-        <v>24.403260639081125</v>
+        <v>18.10188133634929</v>
       </c>
       <c r="D115">
-        <v>81.745172086474199</v>
+        <v>73.117191828301557</v>
       </c>
       <c r="F115" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="G115">
-        <v>24.403260639081125</v>
+        <v>18.10188133634929</v>
       </c>
       <c r="H115">
-        <v>81.745172086474199</v>
+        <v>73.117191828301557</v>
       </c>
     </row>
     <row r="116" spans="2:8">
@@ -33683,19 +33642,19 @@
         <v>502</v>
       </c>
       <c r="C116">
-        <v>21.773659233214904</v>
+        <v>15.819154094000121</v>
       </c>
       <c r="D116">
-        <v>79.634886727627389</v>
+        <v>74.319190274631552</v>
       </c>
       <c r="F116" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="G116">
-        <v>21.773659233214904</v>
+        <v>15.819154094000121</v>
       </c>
       <c r="H116">
-        <v>79.634886727627389</v>
+        <v>74.319190274631552</v>
       </c>
     </row>
     <row r="117" spans="2:8">
@@ -33703,19 +33662,19 @@
         <v>503</v>
       </c>
       <c r="C117">
-        <v>20.962799621758052</v>
+        <v>12.425595365564485</v>
       </c>
       <c r="D117">
-        <v>82.637600142585043</v>
+        <v>77.12049771033233</v>
       </c>
       <c r="F117" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="G117">
-        <v>20.962799621758052</v>
+        <v>12.425595365564485</v>
       </c>
       <c r="H117">
-        <v>82.637600142585043</v>
+        <v>77.12049771033233</v>
       </c>
     </row>
     <row r="118" spans="2:8">
@@ -33723,19 +33682,19 @@
         <v>504</v>
       </c>
       <c r="C118">
-        <v>20.584886838633903</v>
+        <v>14.550177980339036</v>
       </c>
       <c r="D118">
-        <v>80.516222336466086</v>
+        <v>78.639677484304769</v>
       </c>
       <c r="F118" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="G118">
-        <v>20.584886838633903</v>
+        <v>14.550177980339036</v>
       </c>
       <c r="H118">
-        <v>80.516222336466086</v>
+        <v>78.639677484304769</v>
       </c>
     </row>
     <row r="119" spans="2:8">
@@ -33743,19 +33702,19 @@
         <v>505</v>
       </c>
       <c r="C119">
-        <v>19.756636381724764</v>
+        <v>17.542829845456627</v>
       </c>
       <c r="D119">
-        <v>82.149176502195019</v>
+        <v>78.450493396292188</v>
       </c>
       <c r="F119" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="G119">
-        <v>19.756636381724764</v>
+        <v>17.542829845456627</v>
       </c>
       <c r="H119">
-        <v>82.149176502195019</v>
+        <v>78.450493396292188</v>
       </c>
     </row>
     <row r="120" spans="2:8">
@@ -33763,19 +33722,19 @@
         <v>506</v>
       </c>
       <c r="C120">
-        <v>26.444177635438987</v>
+        <v>16.910107120094079</v>
       </c>
       <c r="D120">
-        <v>84.814362991919268</v>
+        <v>76.807084539797074</v>
       </c>
       <c r="F120" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="G120">
-        <v>26.444177635438987</v>
+        <v>16.910107120094079</v>
       </c>
       <c r="H120">
-        <v>84.814362991919268</v>
+        <v>76.807084539797074</v>
       </c>
     </row>
     <row r="121" spans="2:8">
@@ -33783,19 +33742,19 @@
         <v>507</v>
       </c>
       <c r="C121">
-        <v>25.688543313501697</v>
+        <v>18.813105142821843</v>
       </c>
       <c r="D121">
-        <v>84.574649631813244</v>
+        <v>74.473661275825464</v>
       </c>
       <c r="F121" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="G121">
-        <v>25.688543313501697</v>
+        <v>18.813105142821843</v>
       </c>
       <c r="H121">
-        <v>84.574649631813244</v>
+        <v>74.473661275825464</v>
       </c>
     </row>
     <row r="122" spans="2:8">
@@ -33803,19 +33762,19 @@
         <v>508</v>
       </c>
       <c r="C122">
-        <v>24.864264630017956</v>
+        <v>15.649766809815487</v>
       </c>
       <c r="D122">
-        <v>84.068049540960899</v>
+        <v>75.424040724855487</v>
       </c>
       <c r="F122" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="G122">
-        <v>24.864264630017956</v>
+        <v>15.649766809815487</v>
       </c>
       <c r="H122">
-        <v>84.068049540960899</v>
+        <v>75.424040724855487</v>
       </c>
     </row>
     <row r="123" spans="2:8">
@@ -33823,19 +33782,19 @@
         <v>509</v>
       </c>
       <c r="C123">
-        <v>25.390120554977347</v>
+        <v>14.202095073903171</v>
       </c>
       <c r="D123">
-        <v>82.463672409316786</v>
+        <v>79.866875548815287</v>
       </c>
       <c r="F123" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="G123">
-        <v>25.390120554977347</v>
+        <v>14.202095073903171</v>
       </c>
       <c r="H123">
-        <v>82.463672409316786</v>
+        <v>79.866875548815287</v>
       </c>
     </row>
     <row r="124" spans="2:8">
@@ -33843,19 +33802,19 @@
         <v>510</v>
       </c>
       <c r="C124">
-        <v>22.925991025423496</v>
+        <v>11.533505704106645</v>
       </c>
       <c r="D124">
-        <v>84.863533005125817</v>
+        <v>79.33897155145317</v>
       </c>
       <c r="F124" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="G124">
-        <v>22.925991025423496</v>
+        <v>11.533505704106645</v>
       </c>
       <c r="H124">
-        <v>84.863533005125817</v>
+        <v>79.33897155145317</v>
       </c>
     </row>
     <row r="125" spans="2:8">
@@ -33863,19 +33822,19 @@
         <v>511</v>
       </c>
       <c r="C125">
-        <v>24.009329258537434</v>
+        <v>9.5960760827453928</v>
       </c>
       <c r="D125">
-        <v>85.626078256446874</v>
+        <v>78.643107010547567</v>
       </c>
       <c r="F125" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="G125">
-        <v>24.009329258537434</v>
+        <v>9.5960760827453928</v>
       </c>
       <c r="H125">
-        <v>85.626078256446874</v>
+        <v>78.643107010547567</v>
       </c>
     </row>
     <row r="126" spans="2:8">
@@ -33883,19 +33842,19 @@
         <v>512</v>
       </c>
       <c r="C126">
-        <v>23.434164569737867</v>
+        <v>8.7327490443746854</v>
       </c>
       <c r="D126">
-        <v>91.364697610929326</v>
+        <v>77.440191307783152</v>
       </c>
       <c r="F126" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="G126">
-        <v>23.434164569737867</v>
+        <v>8.7327490443746854</v>
       </c>
       <c r="H126">
-        <v>91.364697610929326</v>
+        <v>77.440191307783152</v>
       </c>
     </row>
     <row r="127" spans="2:8">
@@ -33903,19 +33862,19 @@
         <v>513</v>
       </c>
       <c r="C127">
-        <v>22.634024681322742</v>
+        <v>21.155816757932119</v>
       </c>
       <c r="D127">
-        <v>88.276459531453753</v>
+        <v>74.857241285934549</v>
       </c>
       <c r="F127" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="G127">
-        <v>22.634024681322742</v>
+        <v>21.155816757932119</v>
       </c>
       <c r="H127">
-        <v>88.276459531453753</v>
+        <v>74.857241285934549</v>
       </c>
     </row>
     <row r="128" spans="2:8">
@@ -33923,19 +33882,19 @@
         <v>514</v>
       </c>
       <c r="C128">
-        <v>20.106235602515724</v>
+        <v>20.206900055993938</v>
       </c>
       <c r="D128">
-        <v>85.800052197183547</v>
+        <v>76.353024478012046</v>
       </c>
       <c r="F128" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="G128">
-        <v>20.106235602515724</v>
+        <v>20.206900055993938</v>
       </c>
       <c r="H128">
-        <v>85.800052197183547</v>
+        <v>76.353024478012046</v>
       </c>
     </row>
     <row r="129" spans="2:8">
@@ -33943,19 +33902,19 @@
         <v>515</v>
       </c>
       <c r="C129">
-        <v>23.186798131460439</v>
+        <v>21.779166178569184</v>
       </c>
       <c r="D129">
-        <v>87.097363310443356</v>
+        <v>71.045609463613943</v>
       </c>
       <c r="F129" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="G129">
-        <v>23.186798131460439</v>
+        <v>21.779166178569184</v>
       </c>
       <c r="H129">
-        <v>87.097363310443356</v>
+        <v>71.045609463613943</v>
       </c>
     </row>
     <row r="130" spans="2:8">
@@ -33963,19 +33922,19 @@
         <v>516</v>
       </c>
       <c r="C130">
-        <v>24.413894232513851</v>
+        <v>20.942569276881464</v>
       </c>
       <c r="D130">
-        <v>87.713139076831325</v>
+        <v>73.397808100437302</v>
       </c>
       <c r="F130" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="G130">
-        <v>24.413894232513851</v>
+        <v>20.942569276881464</v>
       </c>
       <c r="H130">
-        <v>87.713139076831325</v>
+        <v>73.397808100437302</v>
       </c>
     </row>
     <row r="131" spans="2:8">
@@ -33983,19 +33942,19 @@
         <v>517</v>
       </c>
       <c r="C131">
-        <v>26.066552421403856</v>
+        <v>27.347823277046995</v>
       </c>
       <c r="D131">
-        <v>86.742517984861067</v>
+        <v>70.311592591472788</v>
       </c>
       <c r="F131" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="G131">
-        <v>26.066552421403856</v>
+        <v>27.347823277046995</v>
       </c>
       <c r="H131">
-        <v>86.742517984861067</v>
+        <v>70.311592591472788</v>
       </c>
     </row>
     <row r="132" spans="2:8">
@@ -34003,19 +33962,19 @@
         <v>518</v>
       </c>
       <c r="C132">
-        <v>25.36439741125924</v>
+        <v>27.668212329370533</v>
       </c>
       <c r="D132">
-        <v>88.519468667917849</v>
+        <v>72.586998984902635</v>
       </c>
       <c r="F132" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="G132">
-        <v>25.36439741125924</v>
+        <v>27.668212329370533</v>
       </c>
       <c r="H132">
-        <v>88.519468667917849</v>
+        <v>72.586998984902635</v>
       </c>
     </row>
     <row r="133" spans="2:8">
@@ -34023,19 +33982,19 @@
         <v>519</v>
       </c>
       <c r="C133">
-        <v>17.151776970611138</v>
+        <v>29.808688540741539</v>
       </c>
       <c r="D133">
-        <v>80.642825217012117</v>
+        <v>73.729865416877516</v>
       </c>
       <c r="F133" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="G133">
-        <v>17.151776970611138</v>
+        <v>29.808688540741539</v>
       </c>
       <c r="H133">
-        <v>80.642825217012117</v>
+        <v>73.729865416877516</v>
       </c>
     </row>
     <row r="134" spans="2:8">
@@ -34043,19 +34002,19 @@
         <v>520</v>
       </c>
       <c r="C134">
-        <v>15.731577817652772</v>
+        <v>28.54206364942322</v>
       </c>
       <c r="D134">
-        <v>80.309702751630525</v>
+        <v>73.916253181524226</v>
       </c>
       <c r="F134" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="G134">
-        <v>15.731577817652772</v>
+        <v>28.54206364942322</v>
       </c>
       <c r="H134">
-        <v>80.309702751630525</v>
+        <v>73.916253181524226</v>
       </c>
     </row>
     <row r="135" spans="2:8">
@@ -34063,19 +34022,19 @@
         <v>521</v>
       </c>
       <c r="C135">
-        <v>19.307871111566858</v>
+        <v>25.844148868044844</v>
       </c>
       <c r="D135">
-        <v>79.347299662889384</v>
+        <v>71.642393294309116</v>
       </c>
       <c r="F135" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="G135">
-        <v>19.307871111566858</v>
+        <v>25.844148868044844</v>
       </c>
       <c r="H135">
-        <v>79.347299662889384</v>
+        <v>71.642393294309116</v>
       </c>
     </row>
     <row r="136" spans="2:8">
@@ -34083,19 +34042,19 @@
         <v>522</v>
       </c>
       <c r="C136">
-        <v>18.434863476578929</v>
+        <v>23.537382204563563</v>
       </c>
       <c r="D136">
-        <v>82.35220938638534</v>
+        <v>69.491584547532014</v>
       </c>
       <c r="F136" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="G136">
-        <v>18.434863476578929</v>
+        <v>23.537382204563563</v>
       </c>
       <c r="H136">
-        <v>82.35220938638534</v>
+        <v>69.491584547532014</v>
       </c>
     </row>
     <row r="137" spans="2:8">
@@ -34103,19 +34062,19 @@
         <v>523</v>
       </c>
       <c r="C137">
-        <v>20.873713797988938</v>
+        <v>23.867012447458531</v>
       </c>
       <c r="D137">
-        <v>78.057322734683396</v>
+        <v>71.219253161407536</v>
       </c>
       <c r="F137" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="G137">
-        <v>20.873713797988938</v>
+        <v>23.867012447458531</v>
       </c>
       <c r="H137">
-        <v>78.057322734683396</v>
+        <v>71.219253161407536</v>
       </c>
     </row>
     <row r="138" spans="2:8">
@@ -34123,19 +34082,19 @@
         <v>524</v>
       </c>
       <c r="C138">
-        <v>19.257126862183384</v>
+        <v>23.161319960013007</v>
       </c>
       <c r="D138">
-        <v>74.415531049013609</v>
+        <v>72.89178314089699</v>
       </c>
       <c r="F138" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="G138">
-        <v>19.257126862183384</v>
+        <v>23.161319960013007</v>
       </c>
       <c r="H138">
-        <v>74.415531049013609</v>
+        <v>72.89178314089699</v>
       </c>
     </row>
     <row r="139" spans="2:8">
@@ -34143,19 +34102,19 @@
         <v>525</v>
       </c>
       <c r="C139">
-        <v>20.86372113464547</v>
+        <v>23.62601404726578</v>
       </c>
       <c r="D139">
-        <v>75.788587835847693</v>
+        <v>74.316530316007331</v>
       </c>
       <c r="F139" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="G139">
-        <v>20.86372113464547</v>
+        <v>23.62601404726578</v>
       </c>
       <c r="H139">
-        <v>75.788587835847693</v>
+        <v>74.316530316007331</v>
       </c>
     </row>
     <row r="140" spans="2:8">
@@ -34163,19 +34122,19 @@
         <v>526</v>
       </c>
       <c r="C140">
-        <v>9.5960760827453928</v>
+        <v>22.764211806411765</v>
       </c>
       <c r="D140">
-        <v>78.643107010547567</v>
+        <v>77.120257706706013</v>
       </c>
       <c r="F140" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G140">
-        <v>9.5960760827453928</v>
+        <v>22.764211806411765</v>
       </c>
       <c r="H140">
-        <v>78.643107010547567</v>
+        <v>77.120257706706013</v>
       </c>
     </row>
     <row r="141" spans="2:8">
@@ -34183,19 +34142,19 @@
         <v>527</v>
       </c>
       <c r="C141">
-        <v>11.888456297244469</v>
+        <v>24.020412520611149</v>
       </c>
       <c r="D141">
-        <v>79.433368253396324</v>
+        <v>76.570584902688594</v>
       </c>
       <c r="F141" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="G141">
-        <v>11.888456297244469</v>
+        <v>24.020412520611149</v>
       </c>
       <c r="H141">
-        <v>79.433368253396324</v>
+        <v>76.570584902688594</v>
       </c>
     </row>
     <row r="142" spans="2:8">
@@ -34203,19 +34162,19 @@
         <v>528</v>
       </c>
       <c r="C142">
-        <v>15.200429542357904</v>
+        <v>25.841336832412249</v>
       </c>
       <c r="D142">
-        <v>79.105957638268393</v>
+        <v>74.764996798480269</v>
       </c>
       <c r="F142" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="G142">
-        <v>15.200429542357904</v>
+        <v>25.841336832412249</v>
       </c>
       <c r="H142">
-        <v>79.105957638268393</v>
+        <v>74.764996798480269</v>
       </c>
     </row>
     <row r="143" spans="2:8">
@@ -34223,19 +34182,19 @@
         <v>529</v>
       </c>
       <c r="C143">
-        <v>12.277183904189595</v>
+        <v>26.705063158497371</v>
       </c>
       <c r="D143">
-        <v>78.703731334785473</v>
+        <v>75.718103311208239</v>
       </c>
       <c r="F143" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="G143">
-        <v>12.277183904189595</v>
+        <v>26.705063158497371</v>
       </c>
       <c r="H143">
-        <v>78.703731334785473</v>
+        <v>75.718103311208239</v>
       </c>
     </row>
     <row r="144" spans="2:8">
@@ -34243,19 +34202,19 @@
         <v>530</v>
       </c>
       <c r="C144">
-        <v>17.97193329665479</v>
+        <v>19.778519454413203</v>
       </c>
       <c r="D144">
-        <v>78.158973175470464</v>
+        <v>85.744169475346055</v>
       </c>
       <c r="F144" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="G144">
-        <v>17.97193329665479</v>
+        <v>19.778519454413203</v>
       </c>
       <c r="H144">
-        <v>78.158973175470464</v>
+        <v>85.744169475346055</v>
       </c>
     </row>
     <row r="145" spans="2:8">
@@ -34263,19 +34222,19 @@
         <v>531</v>
       </c>
       <c r="C145">
-        <v>17.301133896012278</v>
+        <v>23.434164569737867</v>
       </c>
       <c r="D145">
-        <v>76.392431566147351</v>
+        <v>91.364697610929326</v>
       </c>
       <c r="F145" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="G145">
-        <v>17.301133896012278</v>
+        <v>23.434164569737867</v>
       </c>
       <c r="H145">
-        <v>76.392431566147351</v>
+        <v>91.364697610929326</v>
       </c>
     </row>
     <row r="146" spans="2:8">
@@ -34283,19 +34242,19 @@
         <v>532</v>
       </c>
       <c r="C146">
-        <v>14.689600757873064</v>
+        <v>23.416858734520115</v>
       </c>
       <c r="D146">
-        <v>77.687512372796817</v>
+        <v>88.021741728573033</v>
       </c>
       <c r="F146" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="G146">
-        <v>14.689600757873064</v>
+        <v>23.416858734520115</v>
       </c>
       <c r="H146">
-        <v>77.687512372796817</v>
+        <v>88.021741728573033</v>
       </c>
     </row>
     <row r="147" spans="2:8">
@@ -34303,19 +34262,19 @@
         <v>533</v>
       </c>
       <c r="C147">
-        <v>18.10188133634929</v>
+        <v>22.250500124823297</v>
       </c>
       <c r="D147">
-        <v>73.117191828301557</v>
+        <v>88.017609000282519</v>
       </c>
       <c r="F147" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="G147">
-        <v>18.10188133634929</v>
+        <v>22.250500124823297</v>
       </c>
       <c r="H147">
-        <v>73.117191828301557</v>
+        <v>88.017609000282519</v>
       </c>
     </row>
     <row r="148" spans="2:8">
@@ -34323,19 +34282,19 @@
         <v>534</v>
       </c>
       <c r="C148">
-        <v>16.397943140481793</v>
+        <v>24.930627855967352</v>
       </c>
       <c r="D148">
-        <v>74.044050798041852</v>
+        <v>88.092629835435545</v>
       </c>
       <c r="F148" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="G148">
-        <v>16.397943140481793</v>
+        <v>24.930627855967352</v>
       </c>
       <c r="H148">
-        <v>74.044050798041852</v>
+        <v>88.092629835435545</v>
       </c>
     </row>
     <row r="149" spans="2:8">
@@ -34343,19 +34302,19 @@
         <v>535</v>
       </c>
       <c r="C149">
-        <v>10.027937903487528</v>
+        <v>25.981759940260336</v>
       </c>
       <c r="D149">
-        <v>77.332804703750128</v>
+        <v>87.933042646001581</v>
       </c>
       <c r="F149" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="G149">
-        <v>10.027937903487528</v>
+        <v>25.981759940260336</v>
       </c>
       <c r="H149">
-        <v>77.332804703750128</v>
+        <v>87.933042646001581</v>
       </c>
     </row>
     <row r="150" spans="2:8">
@@ -34363,19 +34322,19 @@
         <v>536</v>
       </c>
       <c r="C150">
-        <v>12.845887555989639</v>
+        <v>24.438742310878997</v>
       </c>
       <c r="D150">
-        <v>76.610684968333302</v>
+        <v>86.731586168708432</v>
       </c>
       <c r="F150" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="G150">
-        <v>12.845887555989639</v>
+        <v>24.438742310878997</v>
       </c>
       <c r="H150">
-        <v>76.610684968333302</v>
+        <v>86.731586168708432</v>
       </c>
     </row>
     <row r="151" spans="2:8">
@@ -34383,19 +34342,19 @@
         <v>537</v>
       </c>
       <c r="C151">
-        <v>15.430546310682852</v>
+        <v>23.739395610876532</v>
       </c>
       <c r="D151">
-        <v>75.329007834456249</v>
+        <v>85.648859894094272</v>
       </c>
       <c r="F151" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="G151">
-        <v>15.430546310682852</v>
+        <v>23.739395610876532</v>
       </c>
       <c r="H151">
-        <v>75.329007834456249</v>
+        <v>85.648859894094272</v>
       </c>
     </row>
     <row r="152" spans="2:8">
@@ -34403,19 +34362,19 @@
         <v>538</v>
       </c>
       <c r="C152">
-        <v>23.641546613525119</v>
+        <v>28.675336697419748</v>
       </c>
       <c r="D152">
-        <v>69.837381407326902</v>
+        <v>77.206378475969643</v>
       </c>
       <c r="F152" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="G152">
-        <v>23.641546613525119</v>
+        <v>28.675336697419748</v>
       </c>
       <c r="H152">
-        <v>69.837381407326902</v>
+        <v>77.206378475969643</v>
       </c>
     </row>
     <row r="153" spans="2:8">
@@ -34423,19 +34382,19 @@
         <v>539</v>
       </c>
       <c r="C153">
-        <v>20.235293020913748</v>
+        <v>29.785580394435748</v>
       </c>
       <c r="D153">
-        <v>73.337752020795662</v>
+        <v>77.108470507158842</v>
       </c>
       <c r="F153" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="G153">
-        <v>20.235293020913748</v>
+        <v>29.785580394435748</v>
       </c>
       <c r="H153">
-        <v>73.337752020795662</v>
+        <v>77.108470507158842</v>
       </c>
     </row>
     <row r="154" spans="2:8">
@@ -34443,19 +34402,19 @@
         <v>540</v>
       </c>
       <c r="C154">
-        <v>21.79451137025972</v>
+        <v>28.674684289117295</v>
       </c>
       <c r="D154">
-        <v>71.910307761551564</v>
+        <v>78.854484297853048</v>
       </c>
       <c r="F154" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="G154">
-        <v>21.79451137025972</v>
+        <v>28.674684289117295</v>
       </c>
       <c r="H154">
-        <v>71.910307761551564</v>
+        <v>78.854484297853048</v>
       </c>
     </row>
     <row r="155" spans="2:8">
@@ -34463,19 +34422,19 @@
         <v>541</v>
       </c>
       <c r="C155">
-        <v>23.332530133704456</v>
+        <v>27.472156910090767</v>
       </c>
       <c r="D155">
-        <v>73.378772638489167</v>
+        <v>78.778863095358872</v>
       </c>
       <c r="F155" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="G155">
-        <v>23.332530133704456</v>
+        <v>27.472156910090767</v>
       </c>
       <c r="H155">
-        <v>73.378772638489167</v>
+        <v>78.778863095358872</v>
       </c>
     </row>
     <row r="156" spans="2:8">
@@ -34483,19 +34442,19 @@
         <v>542</v>
       </c>
       <c r="C156">
-        <v>26.235298616044037</v>
+        <v>29.758564095811749</v>
       </c>
       <c r="D156">
-        <v>72.547991113350264</v>
+        <v>75.491066578156577</v>
       </c>
       <c r="F156" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="G156">
-        <v>26.235298616044037</v>
+        <v>29.758564095811749</v>
       </c>
       <c r="H156">
-        <v>72.547991113350264</v>
+        <v>75.491066578156577</v>
       </c>
     </row>
     <row r="157" spans="2:8">
@@ -34503,19 +34462,19 @@
         <v>543</v>
       </c>
       <c r="C157">
-        <v>24.684505937472583</v>
+        <v>26.88906112537213</v>
       </c>
       <c r="D157">
-        <v>72.376138727460813</v>
+        <v>77.401966664144197</v>
       </c>
       <c r="F157" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="G157">
-        <v>24.684505937472583</v>
+        <v>26.88906112537213</v>
       </c>
       <c r="H157">
-        <v>72.376138727460813</v>
+        <v>77.401966664144197</v>
       </c>
     </row>
     <row r="158" spans="2:8">
@@ -34523,19 +34482,19 @@
         <v>544</v>
       </c>
       <c r="C158">
-        <v>23.13865428301451</v>
+        <v>28.293682817624759</v>
       </c>
       <c r="D158">
-        <v>78.857355389286042</v>
+        <v>75.709283316468529</v>
       </c>
       <c r="F158" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="G158">
-        <v>23.13865428301451</v>
+        <v>28.293682817624759</v>
       </c>
       <c r="H158">
-        <v>78.857355389286042</v>
+        <v>75.709283316468529</v>
       </c>
     </row>
     <row r="159" spans="2:8">
@@ -34543,19 +34502,19 @@
         <v>545</v>
       </c>
       <c r="C159">
-        <v>22.820378648545816</v>
+        <v>25.877907701141385</v>
       </c>
       <c r="D159">
-        <v>75.952051871277561</v>
+        <v>85.86600946430508</v>
       </c>
       <c r="F159" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="G159">
-        <v>22.820378648545816</v>
+        <v>25.877907701141385</v>
       </c>
       <c r="H159">
-        <v>75.952051871277561</v>
+        <v>85.86600946430508</v>
       </c>
     </row>
     <row r="160" spans="2:8">
@@ -34563,19 +34522,19 @@
         <v>546</v>
       </c>
       <c r="C160">
-        <v>24.161220077291691</v>
+        <v>26.705763894083677</v>
       </c>
       <c r="D160">
-        <v>76.306615158292246</v>
+        <v>83.507576624075199</v>
       </c>
       <c r="F160" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="G160">
-        <v>24.161220077291691</v>
+        <v>26.705763894083677</v>
       </c>
       <c r="H160">
-        <v>76.306615158292246</v>
+        <v>83.507576624075199</v>
       </c>
     </row>
     <row r="161" spans="2:8">
@@ -34583,19 +34542,19 @@
         <v>547</v>
       </c>
       <c r="C161">
-        <v>25.796100801082744</v>
+        <v>27.480738799678608</v>
       </c>
       <c r="D161">
-        <v>74.760560472840439</v>
+        <v>80.716751371122385</v>
       </c>
       <c r="F161" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="G161">
-        <v>25.796100801082744</v>
+        <v>27.480738799678608</v>
       </c>
       <c r="H161">
-        <v>74.760560472840439</v>
+        <v>80.716751371122385</v>
       </c>
     </row>
     <row r="162" spans="2:8">
@@ -34603,19 +34562,19 @@
         <v>548</v>
       </c>
       <c r="C162">
-        <v>26.049462668053657</v>
+        <v>25.254802896666462</v>
       </c>
       <c r="D162">
-        <v>76.349824832698488</v>
+        <v>84.101883963290859</v>
       </c>
       <c r="F162" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="G162">
-        <v>26.049462668053657</v>
+        <v>25.254802896666462</v>
       </c>
       <c r="H162">
-        <v>76.349824832698488</v>
+        <v>84.101883963290859</v>
       </c>
     </row>
     <row r="163" spans="2:8">
@@ -34623,19 +34582,19 @@
         <v>549</v>
       </c>
       <c r="C163">
-        <v>25.61450482481651</v>
+        <v>26.316112387828863</v>
       </c>
       <c r="D163">
-        <v>79.539005682974107</v>
+        <v>80.552528139644522</v>
       </c>
       <c r="F163" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="G163">
-        <v>25.61450482481651</v>
+        <v>26.316112387828863</v>
       </c>
       <c r="H163">
-        <v>79.539005682974107</v>
+        <v>80.552528139644522</v>
       </c>
     </row>
     <row r="164" spans="2:8">
@@ -34643,19 +34602,19 @@
         <v>550</v>
       </c>
       <c r="C164">
-        <v>25.026982238537776</v>
+        <v>25.865693876057371</v>
       </c>
       <c r="D164">
-        <v>78.328118769062314</v>
+        <v>82.184691273926532</v>
       </c>
       <c r="F164" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="G164">
-        <v>25.026982238537776</v>
+        <v>25.865693876057371</v>
       </c>
       <c r="H164">
-        <v>78.328118769062314</v>
+        <v>82.184691273926532</v>
       </c>
     </row>
     <row r="165" spans="2:8">
@@ -34663,19 +34622,19 @@
         <v>551</v>
       </c>
       <c r="C165">
-        <v>29.938128170820484</v>
+        <v>24.557967234305494</v>
       </c>
       <c r="D165">
-        <v>75.419785716757175</v>
+        <v>81.993704388759994</v>
       </c>
       <c r="F165" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="G165">
-        <v>29.938128170820484</v>
+        <v>24.557967234305494</v>
       </c>
       <c r="H165">
-        <v>75.419785716757175</v>
+        <v>81.993704388759994</v>
       </c>
     </row>
     <row r="166" spans="2:8">
@@ -34683,19 +34642,19 @@
         <v>552</v>
       </c>
       <c r="C166">
-        <v>27.120371663022347</v>
+        <v>24.206899938274063</v>
       </c>
       <c r="D166">
-        <v>76.848824901998555</v>
+        <v>80.207230676793614</v>
       </c>
       <c r="F166" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="G166">
-        <v>27.120371663022347</v>
+        <v>24.206899938274063</v>
       </c>
       <c r="H166">
-        <v>76.848824901998555</v>
+        <v>80.207230676793614</v>
       </c>
     </row>
     <row r="167" spans="2:8">
@@ -34703,19 +34662,19 @@
         <v>553</v>
       </c>
       <c r="C167">
-        <v>28.744986231599484</v>
+        <v>23.218073818817498</v>
       </c>
       <c r="D167">
-        <v>75.693889534677325</v>
+        <v>80.651317068900511</v>
       </c>
       <c r="F167" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="G167">
-        <v>28.744986231599484</v>
+        <v>23.218073818817498</v>
       </c>
       <c r="H167">
-        <v>75.693889534677325</v>
+        <v>80.651317068900511</v>
       </c>
     </row>
     <row r="168" spans="2:8">
@@ -34723,19 +34682,19 @@
         <v>554</v>
       </c>
       <c r="C168">
-        <v>27.17014391183822</v>
+        <v>25.913846570056801</v>
       </c>
       <c r="D168">
-        <v>70.583748235256252</v>
+        <v>79.392354876609716</v>
       </c>
       <c r="F168" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="G168">
-        <v>27.17014391183822</v>
+        <v>25.913846570056801</v>
       </c>
       <c r="H168">
-        <v>70.583748235256252</v>
+        <v>79.392354876609716</v>
       </c>
     </row>
     <row r="169" spans="2:8">
@@ -34743,19 +34702,19 @@
         <v>555</v>
       </c>
       <c r="C169">
-        <v>29.159276273167201</v>
+        <v>25.658891382800981</v>
       </c>
       <c r="D169">
-        <v>73.398080587990734</v>
+        <v>78.127315494079511</v>
       </c>
       <c r="F169" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="G169">
-        <v>29.159276273167201</v>
+        <v>25.658891382800981</v>
       </c>
       <c r="H169">
-        <v>73.398080587990734</v>
+        <v>78.127315494079511</v>
       </c>
     </row>
     <row r="170" spans="2:8">
@@ -34763,19 +34722,19 @@
         <v>556</v>
       </c>
       <c r="C170">
-        <v>27.65927345946567</v>
+        <v>24.298768402411401</v>
       </c>
       <c r="D170">
-        <v>75.125044446248808</v>
+        <v>78.675749297627448</v>
       </c>
       <c r="F170" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="G170">
-        <v>27.65927345946567</v>
+        <v>24.298768402411401</v>
       </c>
       <c r="H170">
-        <v>75.125044446248808</v>
+        <v>78.675749297627448</v>
       </c>
     </row>
     <row r="171" spans="2:8">
@@ -34783,19 +34742,19 @@
         <v>557</v>
       </c>
       <c r="C171">
-        <v>27.582754040290936</v>
+        <v>12.831190062359031</v>
       </c>
       <c r="D171">
-        <v>73.375033041660885</v>
+        <v>72.10373153455285</v>
       </c>
       <c r="F171" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="G171">
-        <v>27.582754040290936</v>
+        <v>12.831190062359031</v>
       </c>
       <c r="H171">
-        <v>73.375033041660885</v>
+        <v>72.10373153455285</v>
       </c>
     </row>
     <row r="172" spans="2:8">
@@ -34803,19 +34762,19 @@
         <v>558</v>
       </c>
       <c r="C172">
-        <v>11.068898099656709</v>
+        <v>14.517332833443366</v>
       </c>
       <c r="D172">
-        <v>71.842743304758585</v>
+        <v>73.311612255303388</v>
       </c>
       <c r="F172" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="G172">
-        <v>11.068898099656709</v>
+        <v>14.517332833443366</v>
       </c>
       <c r="H172">
-        <v>71.842743304758585</v>
+        <v>73.311612255303388</v>
       </c>
     </row>
     <row r="173" spans="2:8">
@@ -34823,19 +34782,19 @@
         <v>559</v>
       </c>
       <c r="C173">
-        <v>12.890615551378485</v>
+        <v>16.246545066428236</v>
       </c>
       <c r="D173">
-        <v>72.133385027577177</v>
+        <v>72.547721549064121</v>
       </c>
       <c r="F173" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="G173">
-        <v>12.890615551378485</v>
+        <v>16.246545066428236</v>
       </c>
       <c r="H173">
-        <v>72.133385027577177</v>
+        <v>72.547721549064121</v>
       </c>
     </row>
     <row r="174" spans="2:8">
@@ -34843,19 +34802,19 @@
         <v>560</v>
       </c>
       <c r="C174">
-        <v>14.500870941812488</v>
+        <v>21.443683766845677</v>
       </c>
       <c r="D174">
-        <v>73.301161934079801</v>
+        <v>68.637474643362168</v>
       </c>
       <c r="F174" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="G174">
-        <v>14.500870941812488</v>
+        <v>21.443683766845677</v>
       </c>
       <c r="H174">
-        <v>73.301161934079801</v>
+        <v>68.637474643362168</v>
       </c>
     </row>
     <row r="175" spans="2:8">
@@ -34863,19 +34822,19 @@
         <v>561</v>
       </c>
       <c r="C175">
-        <v>16.937858360197275</v>
+        <v>22.459981324731164</v>
       </c>
       <c r="D175">
-        <v>72.383149970196371</v>
+        <v>67.816370188269687</v>
       </c>
       <c r="F175" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G175">
-        <v>16.937858360197275</v>
+        <v>22.459981324731164</v>
       </c>
       <c r="H175">
-        <v>72.383149970196371</v>
+        <v>67.816370188269687</v>
       </c>
     </row>
     <row r="176" spans="2:8">
@@ -34883,19 +34842,19 @@
         <v>562</v>
       </c>
       <c r="C176">
-        <v>15.580799251375479</v>
+        <v>18.473437408178992</v>
       </c>
       <c r="D176">
-        <v>72.885826415852506</v>
+        <v>71.476213429601088</v>
       </c>
       <c r="F176" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="G176">
-        <v>15.580799251375479</v>
+        <v>18.473437408178992</v>
       </c>
       <c r="H176">
-        <v>72.885826415852506</v>
+        <v>71.476213429601088</v>
       </c>
     </row>
     <row r="177" spans="2:8">
@@ -34903,19 +34862,19 @@
         <v>563</v>
       </c>
       <c r="C177">
-        <v>22.564386597052057</v>
+        <v>17.766068597117588</v>
       </c>
       <c r="D177">
-        <v>67.565303942781298</v>
+        <v>72.258641968560795</v>
       </c>
       <c r="F177" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="G177">
-        <v>22.564386597052057</v>
+        <v>17.766068597117588</v>
       </c>
       <c r="H177">
-        <v>67.565303942781298</v>
+        <v>72.258641968560795</v>
       </c>
     </row>
     <row r="178" spans="2:8">
@@ -34923,19 +34882,19 @@
         <v>564</v>
       </c>
       <c r="C178">
-        <v>21.843450436836243</v>
+        <v>19.725003417896119</v>
       </c>
       <c r="D178">
-        <v>68.369225508640312</v>
+        <v>70.211779042366572</v>
       </c>
       <c r="F178" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="G178">
-        <v>21.843450436836243</v>
+        <v>19.725003417896119</v>
       </c>
       <c r="H178">
-        <v>68.369225508640312</v>
+        <v>70.211779042366572</v>
       </c>
     </row>
     <row r="179" spans="2:8">
@@ -34943,19 +34902,19 @@
         <v>565</v>
       </c>
       <c r="C179">
-        <v>18.362408966417828</v>
+        <v>19.498634613717769</v>
       </c>
       <c r="D179">
-        <v>71.687323687255343</v>
+        <v>71.468485531282241</v>
       </c>
       <c r="F179" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="G179">
-        <v>18.362408966417828</v>
+        <v>19.498634613717769</v>
       </c>
       <c r="H179">
-        <v>71.687323687255343</v>
+        <v>71.468485531282241</v>
       </c>
     </row>
     <row r="180" spans="2:8">
@@ -34963,19 +34922,19 @@
         <v>566</v>
       </c>
       <c r="C180">
-        <v>20.563098426100865</v>
+        <v>20.664319816781006</v>
       </c>
       <c r="D180">
-        <v>69.523978949454545</v>
+        <v>70.052771659579804</v>
       </c>
       <c r="F180" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="G180">
-        <v>20.563098426100865</v>
+        <v>20.664319816781006</v>
       </c>
       <c r="H180">
-        <v>69.523978949454545</v>
+        <v>70.052771659579804</v>
       </c>
     </row>
     <row r="181" spans="2:8">
@@ -34983,19 +34942,19 @@
         <v>567</v>
       </c>
       <c r="C181">
-        <v>19.444057687436462</v>
+        <v>20.466992894954146</v>
       </c>
       <c r="D181">
-        <v>70.489223393236372</v>
+        <v>88.259977445722924</v>
       </c>
       <c r="F181" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="G181">
-        <v>19.444057687436462</v>
+        <v>20.466992894954146</v>
       </c>
       <c r="H181">
-        <v>70.489223393236372</v>
+        <v>88.259977445722924</v>
       </c>
     </row>
     <row r="182" spans="2:8">
@@ -35003,19 +34962,19 @@
         <v>568</v>
       </c>
       <c r="C182">
-        <v>20.371266713121692</v>
+        <v>20.697238047149398</v>
       </c>
       <c r="D182">
-        <v>70.585247722248056</v>
+        <v>89.249853772557117</v>
       </c>
       <c r="F182" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="G182">
-        <v>20.371266713121692</v>
+        <v>20.697238047149398</v>
       </c>
       <c r="H182">
-        <v>70.585247722248056</v>
+        <v>89.249853772557117</v>
       </c>
     </row>
     <row r="183" spans="2:8">
@@ -35023,19 +34982,19 @@
         <v>569</v>
       </c>
       <c r="C183">
-        <v>19.498634613717769</v>
+        <v>18.124069545734084</v>
       </c>
       <c r="D183">
-        <v>71.468485531282241</v>
+        <v>84.322741673740026</v>
       </c>
       <c r="F183" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="G183">
-        <v>19.498634613717769</v>
+        <v>18.124069545734084</v>
       </c>
       <c r="H183">
-        <v>71.468485531282241</v>
+        <v>84.322741673740026</v>
       </c>
     </row>
     <row r="184" spans="2:8">
@@ -35043,19 +35002,19 @@
         <v>570</v>
       </c>
       <c r="C184">
-        <v>12.57199809549796</v>
+        <v>20.209245969976315</v>
       </c>
       <c r="D184">
-        <v>80.504533392317782</v>
+        <v>87.287671092538389</v>
       </c>
       <c r="F184" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="G184">
-        <v>12.57199809549796</v>
+        <v>20.209245969976315</v>
       </c>
       <c r="H184">
-        <v>80.504533392317782</v>
+        <v>87.287671092538389</v>
       </c>
     </row>
     <row r="185" spans="2:8">
@@ -35063,19 +35022,19 @@
         <v>571</v>
       </c>
       <c r="C185">
-        <v>10.58438967691929</v>
+        <v>19.199648568189559</v>
       </c>
       <c r="D185">
-        <v>80.410720845682292</v>
+        <v>85.488721040356282</v>
       </c>
       <c r="F185" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="G185">
-        <v>10.58438967691929</v>
+        <v>19.199648568189559</v>
       </c>
       <c r="H185">
-        <v>80.410720845682292</v>
+        <v>85.488721040356282</v>
       </c>
     </row>
     <row r="186" spans="2:8">
@@ -35083,19 +35042,19 @@
         <v>572</v>
       </c>
       <c r="C186">
-        <v>11.427190805917643</v>
+        <v>8.5816869575851111</v>
       </c>
       <c r="D186">
-        <v>79.947634935599766</v>
+        <v>78.91520492542935</v>
       </c>
       <c r="F186" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="G186">
-        <v>11.427190805917643</v>
+        <v>8.5816869575851111</v>
       </c>
       <c r="H186">
-        <v>79.947634935599766</v>
+        <v>78.91520492542935</v>
       </c>
     </row>
     <row r="187" spans="2:8">
@@ -35103,19 +35062,19 @@
         <v>573</v>
       </c>
       <c r="C187">
-        <v>8.5816869575851111</v>
+        <v>7.3707188726535096</v>
       </c>
       <c r="D187">
-        <v>78.91520492542935</v>
+        <v>77.418385659092905</v>
       </c>
       <c r="F187" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="G187">
-        <v>8.5816869575851111</v>
+        <v>7.3707188726535096</v>
       </c>
       <c r="H187">
-        <v>78.91520492542935</v>
+        <v>77.418385659092905</v>
       </c>
     </row>
     <row r="188" spans="2:8">
@@ -35129,7 +35088,7 @@
         <v>77.016592958785239</v>
       </c>
       <c r="F188" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="G188">
         <v>7.7966596562838326</v>
@@ -35143,19 +35102,19 @@
         <v>575</v>
       </c>
       <c r="C189">
-        <v>7.3707188726535096</v>
+        <v>12.756467098170049</v>
       </c>
       <c r="D189">
-        <v>77.418385659092905</v>
+        <v>80.485970658506119</v>
       </c>
       <c r="F189" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="G189">
-        <v>7.3707188726535096</v>
+        <v>12.756467098170049</v>
       </c>
       <c r="H189">
-        <v>77.418385659092905</v>
+        <v>80.485970658506119</v>
       </c>
     </row>
     <row r="190" spans="2:8">
@@ -35163,19 +35122,19 @@
         <v>576</v>
       </c>
       <c r="C190">
-        <v>15.257020235184816</v>
+        <v>10.58438967691929</v>
       </c>
       <c r="D190">
-        <v>80.712625172486895</v>
+        <v>80.410720845682292</v>
       </c>
       <c r="F190" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="G190">
-        <v>15.257020235184816</v>
+        <v>10.58438967691929</v>
       </c>
       <c r="H190">
-        <v>80.712625172486895</v>
+        <v>80.410720845682292</v>
       </c>
     </row>
     <row r="191" spans="2:8">
@@ -35183,19 +35142,19 @@
         <v>577</v>
       </c>
       <c r="C191">
-        <v>17.854854322167657</v>
+        <v>11.43036770345066</v>
       </c>
       <c r="D191">
-        <v>83.945608235027095</v>
+        <v>79.983076681947793</v>
       </c>
       <c r="F191" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="G191">
-        <v>17.854854322167657</v>
+        <v>11.43036770345066</v>
       </c>
       <c r="H191">
-        <v>83.945608235027095</v>
+        <v>79.983076681947793</v>
       </c>
     </row>
     <row r="192" spans="2:8">
@@ -35203,19 +35162,19 @@
         <v>578</v>
       </c>
       <c r="C192">
-        <v>16.760193191518969</v>
+        <v>16.772624744207636</v>
       </c>
       <c r="D192">
-        <v>82.735576508982589</v>
+        <v>82.70745157151454</v>
       </c>
       <c r="F192" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="G192">
-        <v>16.760193191518969</v>
+        <v>16.772624744207636</v>
       </c>
       <c r="H192">
-        <v>82.735576508982589</v>
+        <v>82.70745157151454</v>
       </c>
     </row>
     <row r="193" spans="2:8">
@@ -35223,19 +35182,19 @@
         <v>579</v>
       </c>
       <c r="C193">
-        <v>20.60369682782548</v>
+        <v>14.271648656886221</v>
       </c>
       <c r="D193">
-        <v>88.817161425025134</v>
+        <v>80.398912703831485</v>
       </c>
       <c r="F193" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="G193">
-        <v>20.60369682782548</v>
+        <v>14.271648656886221</v>
       </c>
       <c r="H193">
-        <v>88.817161425025134</v>
+        <v>80.398912703831485</v>
       </c>
     </row>
     <row r="194" spans="2:8">
@@ -35243,39 +35202,19 @@
         <v>580</v>
       </c>
       <c r="C194">
-        <v>20.113583370257921</v>
+        <v>15.356907810679193</v>
       </c>
       <c r="D194">
-        <v>87.205281355072941</v>
+        <v>80.755419008527241</v>
       </c>
       <c r="F194" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="G194">
-        <v>20.113583370257921</v>
+        <v>15.356907810679193</v>
       </c>
       <c r="H194">
-        <v>87.205281355072941</v>
-      </c>
-    </row>
-    <row r="195" spans="2:8">
-      <c r="B195" t="s">
-        <v>581</v>
-      </c>
-      <c r="C195">
-        <v>18.969725043879009</v>
-      </c>
-      <c r="D195">
-        <v>85.22771297280012</v>
-      </c>
-      <c r="F195" t="s">
-        <v>984</v>
-      </c>
-      <c r="G195">
-        <v>18.969725043879009</v>
-      </c>
-      <c r="H195">
-        <v>85.22771297280012</v>
+        <v>80.755419008527241</v>
       </c>
     </row>
   </sheetData>
